--- a/datos/casos_corrupcion_chile.xlsx
+++ b/datos/casos_corrupcion_chile.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="712">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="713">
   <si>
     <t>Caso</t>
   </si>
@@ -1253,6 +1253,17 @@
         <rFont val="Helvetica Neue"/>
       </rPr>
       <t>https://www.latercera.com/nacional/noticia/vina-del-mar-auditoria-revela-pago-por-23-mil-millones-en-horas-extra-entre-2016-y-2021/5VDK6NYAHRDCBGSIOJW4XFR26M/?outputType=base-amp-type</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <u val="single"/>
+        <sz val="10"/>
+        <color indexed="8"/>
+        <rFont val="Helvetica Neue"/>
+      </rPr>
+      <t>https://contrapoderchile.cl/fiscalia-confirma-que-virginia-reginato-udi-esta-en-calidad-de-imputada-por-fraude-al-fisco/</t>
     </r>
   </si>
   <si>
@@ -7514,11 +7525,13 @@
       <c r="X46" t="s" s="19">
         <v>272</v>
       </c>
-      <c r="Y46" s="18"/>
+      <c r="Y46" t="s" s="19">
+        <v>273</v>
+      </c>
     </row>
     <row r="47" ht="32.05" customHeight="1">
       <c r="A47" t="s" s="13">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="B47" s="14">
         <v>10210000000</v>
@@ -7527,7 +7540,7 @@
         <v>2021</v>
       </c>
       <c r="D47" t="s" s="17">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="E47" t="s" s="17">
         <v>70</v>
@@ -7542,7 +7555,7 @@
         <v>2020</v>
       </c>
       <c r="I47" t="s" s="17">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="J47" t="s" s="17">
         <v>99</v>
@@ -7555,7 +7568,7 @@
       <c r="N47" s="16"/>
       <c r="O47" s="18"/>
       <c r="P47" t="s" s="19">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="Q47" t="s" s="19">
         <v>134</v>
@@ -7564,7 +7577,7 @@
       <c r="S47" s="16"/>
       <c r="T47" s="16"/>
       <c r="U47" t="s" s="19">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="V47" s="18"/>
       <c r="W47" s="18"/>
@@ -7573,7 +7586,7 @@
     </row>
     <row r="48" ht="32.05" customHeight="1">
       <c r="A48" t="s" s="13">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="B48" s="14">
         <v>351000000</v>
@@ -7582,13 +7595,13 @@
         <v>2021</v>
       </c>
       <c r="D48" t="s" s="17">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="E48" t="s" s="17">
         <v>27</v>
       </c>
       <c r="F48" t="s" s="17">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="G48" s="15">
         <v>2013</v>
@@ -7597,7 +7610,7 @@
         <v>2016</v>
       </c>
       <c r="I48" t="s" s="17">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="J48" t="s" s="17">
         <v>99</v>
@@ -7615,16 +7628,16 @@
       </c>
       <c r="R48" s="16"/>
       <c r="S48" t="s" s="17">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="T48" t="s" s="17">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="U48" t="s" s="17">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="V48" t="s" s="19">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="W48" s="18"/>
       <c r="X48" s="18"/>
@@ -7632,7 +7645,7 @@
     </row>
     <row r="49" ht="20.05" customHeight="1">
       <c r="A49" t="s" s="13">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="B49" s="14">
         <v>264254000</v>
@@ -7641,7 +7654,7 @@
         <v>2021</v>
       </c>
       <c r="D49" t="s" s="17">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="E49" t="s" s="17">
         <v>27</v>
@@ -7666,7 +7679,7 @@
       <c r="S49" s="16"/>
       <c r="T49" s="16"/>
       <c r="U49" t="s" s="19">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="V49" s="18"/>
       <c r="W49" s="18"/>
@@ -7675,7 +7688,7 @@
     </row>
     <row r="50" ht="20.05" customHeight="1">
       <c r="A50" t="s" s="13">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="B50" s="14">
         <v>188000000</v>
@@ -7684,7 +7697,7 @@
         <v>2021</v>
       </c>
       <c r="D50" t="s" s="17">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="E50" t="s" s="17">
         <v>27</v>
@@ -7706,7 +7719,7 @@
       <c r="N50" s="16"/>
       <c r="O50" s="18"/>
       <c r="P50" t="s" s="19">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="Q50" s="18"/>
       <c r="R50" s="16"/>
@@ -7722,7 +7735,7 @@
     </row>
     <row r="51" ht="32.35" customHeight="1">
       <c r="A51" t="s" s="21">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="B51" s="22">
         <v>146000000</v>
@@ -7731,7 +7744,7 @@
         <v>2021</v>
       </c>
       <c r="D51" t="s" s="24">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="E51" t="s" s="24">
         <v>32</v>
@@ -7745,7 +7758,7 @@
       </c>
       <c r="I51" s="25"/>
       <c r="J51" t="s" s="24">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="K51" s="25"/>
       <c r="L51" s="25"/>
@@ -7753,29 +7766,29 @@
       <c r="N51" s="25"/>
       <c r="O51" s="26"/>
       <c r="P51" t="s" s="27">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="Q51" s="26"/>
       <c r="R51" s="25"/>
       <c r="S51" s="25"/>
       <c r="T51" t="s" s="24">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="U51" t="s" s="27">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="V51" t="s" s="27">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="W51" t="s" s="27">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="X51" s="26"/>
       <c r="Y51" s="26"/>
     </row>
     <row r="52" ht="32.35" customHeight="1">
       <c r="A52" t="s" s="21">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="B52" s="29"/>
       <c r="C52" s="23">
@@ -7796,7 +7809,7 @@
       <c r="L52" s="25"/>
       <c r="M52" s="25"/>
       <c r="N52" t="s" s="24">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="O52" s="26"/>
       <c r="P52" s="26"/>
@@ -7805,7 +7818,7 @@
       <c r="S52" s="16"/>
       <c r="T52" s="25"/>
       <c r="U52" t="s" s="27">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="V52" s="26"/>
       <c r="W52" s="26"/>
@@ -7814,7 +7827,7 @@
     </row>
     <row r="53" ht="32.05" customHeight="1">
       <c r="A53" t="s" s="13">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="B53" s="14">
         <v>2492000000</v>
@@ -7823,7 +7836,7 @@
         <v>2022</v>
       </c>
       <c r="D53" t="s" s="17">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="E53" t="s" s="17">
         <v>37</v>
@@ -7838,7 +7851,7 @@
         <v>2021</v>
       </c>
       <c r="I53" t="s" s="17">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="J53" t="s" s="17">
         <v>99</v>
@@ -7849,29 +7862,29 @@
       <c r="N53" s="16"/>
       <c r="O53" s="18"/>
       <c r="P53" t="s" s="19">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="Q53" s="18"/>
       <c r="R53" s="16"/>
       <c r="S53" s="16"/>
       <c r="T53" s="16"/>
       <c r="U53" t="s" s="19">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="V53" t="s" s="19">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="W53" t="s" s="19">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="X53" t="s" s="19">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="Y53" s="18"/>
     </row>
     <row r="54" ht="32.35" customHeight="1">
       <c r="A54" t="s" s="21">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="B54" s="22">
         <v>1316591501</v>
@@ -7880,7 +7893,7 @@
         <v>2022</v>
       </c>
       <c r="D54" t="s" s="24">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="E54" t="s" s="24">
         <v>70</v>
@@ -7895,7 +7908,7 @@
         <v>2022</v>
       </c>
       <c r="I54" t="s" s="24">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="J54" t="s" s="24">
         <v>99</v>
@@ -7906,19 +7919,19 @@
       <c r="N54" s="25"/>
       <c r="O54" s="26"/>
       <c r="P54" t="s" s="27">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="Q54" t="s" s="27">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="R54" s="25"/>
       <c r="S54" s="16"/>
       <c r="T54" s="25"/>
       <c r="U54" t="s" s="27">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="V54" t="s" s="27">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="W54" s="26"/>
       <c r="X54" s="26"/>
@@ -7926,7 +7939,7 @@
     </row>
     <row r="55" ht="32.35" customHeight="1">
       <c r="A55" t="s" s="21">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="B55" s="22">
         <v>1291937035</v>
@@ -7935,13 +7948,13 @@
         <v>2022</v>
       </c>
       <c r="D55" t="s" s="24">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="E55" t="s" s="24">
         <v>37</v>
       </c>
       <c r="F55" t="s" s="24">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="G55" s="23">
         <v>2020</v>
@@ -7966,20 +7979,20 @@
       <c r="S55" s="16"/>
       <c r="T55" s="25"/>
       <c r="U55" t="s" s="27">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="V55" t="s" s="27">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="W55" t="s" s="27">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="X55" s="26"/>
       <c r="Y55" s="26"/>
     </row>
     <row r="56" ht="32.05" customHeight="1">
       <c r="A56" t="s" s="13">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="B56" s="14">
         <v>1100000000</v>
@@ -7988,7 +8001,7 @@
         <v>2022</v>
       </c>
       <c r="D56" t="s" s="17">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="E56" t="s" s="17">
         <v>27</v>
@@ -8003,7 +8016,7 @@
         <v>2023</v>
       </c>
       <c r="I56" t="s" s="17">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="J56" t="s" s="17">
         <v>99</v>
@@ -8016,27 +8029,27 @@
       <c r="N56" s="16"/>
       <c r="O56" s="18"/>
       <c r="P56" t="s" s="19">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="Q56" s="18"/>
       <c r="R56" s="16"/>
       <c r="S56" s="16"/>
       <c r="T56" s="16"/>
       <c r="U56" t="s" s="19">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="V56" t="s" s="19">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="W56" t="s" s="19">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="X56" s="18"/>
       <c r="Y56" s="18"/>
     </row>
     <row r="57" ht="20.05" customHeight="1">
       <c r="A57" t="s" s="13">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="B57" s="14">
         <v>200000000</v>
@@ -8045,7 +8058,7 @@
         <v>2022</v>
       </c>
       <c r="D57" t="s" s="17">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="E57" t="s" s="17">
         <v>27</v>
@@ -8060,7 +8073,7 @@
         <v>2021</v>
       </c>
       <c r="I57" t="s" s="17">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="J57" t="s" s="17">
         <v>99</v>
@@ -8078,20 +8091,20 @@
       <c r="S57" s="16"/>
       <c r="T57" s="16"/>
       <c r="U57" t="s" s="19">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="V57" t="s" s="19">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="W57" t="s" s="19">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="X57" s="18"/>
       <c r="Y57" s="18"/>
     </row>
     <row r="58" ht="68.05" customHeight="1">
       <c r="A58" t="s" s="13">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="B58" s="14">
         <v>24000000</v>
@@ -8100,13 +8113,13 @@
         <v>2022</v>
       </c>
       <c r="D58" t="s" s="17">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="E58" t="s" s="17">
         <v>27</v>
       </c>
       <c r="F58" t="s" s="17">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="G58" s="15">
         <v>2015</v>
@@ -8131,30 +8144,30 @@
         <v>72</v>
       </c>
       <c r="Q58" t="s" s="19">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="R58" s="16"/>
       <c r="S58" t="s" s="17">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="T58" t="s" s="17">
         <v>124</v>
       </c>
       <c r="U58" t="s" s="19">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="V58" t="s" s="19">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="W58" t="s" s="19">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="X58" s="18"/>
       <c r="Y58" s="18"/>
     </row>
     <row r="59" ht="20.35" customHeight="1">
       <c r="A59" t="s" s="21">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="B59" s="14">
         <v>7000000</v>
@@ -8163,7 +8176,7 @@
         <v>2022</v>
       </c>
       <c r="D59" t="s" s="24">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="E59" s="25"/>
       <c r="F59" s="25"/>
@@ -8177,7 +8190,7 @@
         <v>193</v>
       </c>
       <c r="J59" t="s" s="24">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="K59" t="s" s="17">
         <v>100</v>
@@ -8187,17 +8200,17 @@
       <c r="N59" s="25"/>
       <c r="O59" s="26"/>
       <c r="P59" t="s" s="27">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="Q59" s="26"/>
       <c r="R59" s="25"/>
       <c r="S59" s="16"/>
       <c r="T59" s="25"/>
       <c r="U59" t="s" s="27">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="V59" t="s" s="27">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="W59" s="26"/>
       <c r="X59" s="26"/>
@@ -8205,7 +8218,7 @@
     </row>
     <row r="60" ht="20.05" customHeight="1">
       <c r="A60" t="s" s="13">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="B60" s="14">
         <v>8713407156</v>
@@ -8230,14 +8243,14 @@
       <c r="N60" s="16"/>
       <c r="O60" s="18"/>
       <c r="P60" t="s" s="19">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="Q60" s="18"/>
       <c r="R60" s="16"/>
       <c r="S60" s="16"/>
       <c r="T60" s="16"/>
       <c r="U60" t="s" s="19">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="V60" s="18"/>
       <c r="W60" s="18"/>
@@ -8246,7 +8259,7 @@
     </row>
     <row r="61" ht="20.05" customHeight="1">
       <c r="A61" t="s" s="13">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="B61" s="14">
         <v>4500000000</v>
@@ -8255,7 +8268,7 @@
         <v>2023</v>
       </c>
       <c r="D61" t="s" s="17">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="E61" t="s" s="17">
         <v>27</v>
@@ -8266,7 +8279,7 @@
       <c r="G61" s="16"/>
       <c r="H61" s="16"/>
       <c r="I61" t="s" s="17">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="J61" t="s" s="17">
         <v>99</v>
@@ -8285,25 +8298,25 @@
       <c r="R61" s="16"/>
       <c r="S61" s="16"/>
       <c r="T61" t="s" s="17">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="U61" t="s" s="19">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="V61" t="s" s="19">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="W61" t="s" s="19">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="X61" t="s" s="19">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="Y61" s="18"/>
     </row>
     <row r="62" ht="20.35" customHeight="1">
       <c r="A62" t="s" s="30">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="B62" s="31">
         <v>2500000000</v>
@@ -8319,7 +8332,7 @@
       <c r="G62" s="25"/>
       <c r="H62" s="25"/>
       <c r="I62" t="s" s="24">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="J62" t="s" s="24">
         <v>14</v>
@@ -8329,7 +8342,7 @@
       <c r="M62" s="25"/>
       <c r="N62" s="25"/>
       <c r="O62" t="s" s="27">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="P62" s="26"/>
       <c r="Q62" s="26"/>
@@ -8337,10 +8350,10 @@
       <c r="S62" s="25"/>
       <c r="T62" s="25"/>
       <c r="U62" t="s" s="27">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="V62" t="s" s="27">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="W62" s="26"/>
       <c r="X62" s="26"/>
@@ -8348,7 +8361,7 @@
     </row>
     <row r="63" ht="32.35" customHeight="1">
       <c r="A63" t="s" s="30">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="B63" s="31">
         <v>2113000000</v>
@@ -8357,18 +8370,18 @@
         <v>2023</v>
       </c>
       <c r="D63" t="s" s="24">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="E63" t="s" s="24">
         <v>27</v>
       </c>
       <c r="F63" t="s" s="24">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="G63" s="25"/>
       <c r="H63" s="25"/>
       <c r="I63" t="s" s="24">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="J63" t="s" s="24">
         <v>14</v>
@@ -8378,30 +8391,30 @@
       <c r="M63" s="25"/>
       <c r="N63" s="25"/>
       <c r="O63" t="s" s="27">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="P63" t="s" s="27">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="Q63" s="26"/>
       <c r="R63" s="25"/>
       <c r="S63" s="25"/>
       <c r="T63" s="25"/>
       <c r="U63" t="s" s="27">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="V63" t="s" s="27">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="W63" t="s" s="27">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="X63" s="26"/>
       <c r="Y63" s="26"/>
     </row>
     <row r="64" ht="20.05" customHeight="1">
       <c r="A64" t="s" s="13">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="B64" s="14">
         <v>2000000000</v>
@@ -8410,13 +8423,13 @@
         <v>2023</v>
       </c>
       <c r="D64" t="s" s="17">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="E64" t="s" s="17">
         <v>27</v>
       </c>
       <c r="F64" t="s" s="17">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="G64" s="15">
         <v>2018</v>
@@ -8425,7 +8438,7 @@
         <v>2019</v>
       </c>
       <c r="I64" t="s" s="17">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="J64" t="s" s="17">
         <v>99</v>
@@ -8436,17 +8449,17 @@
       <c r="N64" s="16"/>
       <c r="O64" s="18"/>
       <c r="P64" t="s" s="19">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="Q64" s="18"/>
       <c r="R64" s="16"/>
       <c r="S64" s="16"/>
       <c r="T64" s="16"/>
       <c r="U64" t="s" s="19">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="V64" t="s" s="19">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="W64" s="18"/>
       <c r="X64" s="18"/>
@@ -8454,7 +8467,7 @@
     </row>
     <row r="65" ht="20.35" customHeight="1">
       <c r="A65" t="s" s="21">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="B65" s="22">
         <v>1683000000</v>
@@ -8463,7 +8476,7 @@
         <v>2023</v>
       </c>
       <c r="D65" t="s" s="24">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="E65" t="s" s="24">
         <v>37</v>
@@ -8484,10 +8497,10 @@
       <c r="M65" s="25"/>
       <c r="N65" s="25"/>
       <c r="O65" t="s" s="27">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="P65" t="s" s="27">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="Q65" t="s" s="27">
         <v>134</v>
@@ -8496,20 +8509,20 @@
       <c r="S65" s="16"/>
       <c r="T65" s="25"/>
       <c r="U65" t="s" s="27">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="V65" t="s" s="27">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="W65" t="s" s="27">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="X65" s="26"/>
       <c r="Y65" s="26"/>
     </row>
     <row r="66" ht="32.35" customHeight="1">
       <c r="A66" t="s" s="21">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="B66" s="22">
         <v>1600000000</v>
@@ -8525,7 +8538,7 @@
       <c r="G66" s="25"/>
       <c r="H66" s="25"/>
       <c r="I66" t="s" s="24">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="J66" t="s" s="24">
         <v>14</v>
@@ -8535,7 +8548,7 @@
       <c r="M66" s="25"/>
       <c r="N66" s="25"/>
       <c r="O66" t="s" s="32">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="P66" s="26"/>
       <c r="Q66" s="26"/>
@@ -8543,7 +8556,7 @@
       <c r="S66" s="25"/>
       <c r="T66" s="25"/>
       <c r="U66" t="s" s="27">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="V66" s="26"/>
       <c r="W66" s="26"/>
@@ -8552,7 +8565,7 @@
     </row>
     <row r="67" ht="32.35" customHeight="1">
       <c r="A67" t="s" s="21">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="B67" s="22">
         <v>1200000000</v>
@@ -8566,7 +8579,7 @@
       <c r="G67" s="25"/>
       <c r="H67" s="25"/>
       <c r="I67" t="s" s="24">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="J67" t="s" s="24">
         <v>14</v>
@@ -8576,7 +8589,7 @@
       <c r="M67" s="25"/>
       <c r="N67" s="25"/>
       <c r="O67" t="s" s="32">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="P67" s="26"/>
       <c r="Q67" s="26"/>
@@ -8584,7 +8597,7 @@
       <c r="S67" s="25"/>
       <c r="T67" s="25"/>
       <c r="U67" t="s" s="27">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="V67" s="26"/>
       <c r="W67" s="26"/>
@@ -8593,7 +8606,7 @@
     </row>
     <row r="68" ht="20.35" customHeight="1">
       <c r="A68" t="s" s="21">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="B68" s="22">
         <v>1200000000</v>
@@ -8609,7 +8622,7 @@
       <c r="G68" s="25"/>
       <c r="H68" s="25"/>
       <c r="I68" t="s" s="24">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="J68" t="s" s="24">
         <v>14</v>
@@ -8619,7 +8632,7 @@
       <c r="M68" s="25"/>
       <c r="N68" s="25"/>
       <c r="O68" t="s" s="27">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="P68" s="26"/>
       <c r="Q68" s="26"/>
@@ -8627,10 +8640,10 @@
       <c r="S68" s="25"/>
       <c r="T68" s="25"/>
       <c r="U68" t="s" s="27">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="V68" t="s" s="27">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="W68" s="26"/>
       <c r="X68" s="26"/>
@@ -8638,7 +8651,7 @@
     </row>
     <row r="69" ht="20.05" customHeight="1">
       <c r="A69" t="s" s="13">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="B69" s="14">
         <v>1160000000</v>
@@ -8647,7 +8660,7 @@
         <v>2023</v>
       </c>
       <c r="D69" t="s" s="17">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="E69" t="s" s="17">
         <v>27</v>
@@ -8658,7 +8671,7 @@
       <c r="G69" s="16"/>
       <c r="H69" s="16"/>
       <c r="I69" t="s" s="17">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="J69" t="s" s="17">
         <v>99</v>
@@ -8671,7 +8684,7 @@
       <c r="N69" s="16"/>
       <c r="O69" s="18"/>
       <c r="P69" t="s" s="19">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="Q69" t="s" s="19">
         <v>260</v>
@@ -8680,20 +8693,20 @@
       <c r="S69" s="16"/>
       <c r="T69" s="16"/>
       <c r="U69" t="s" s="19">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="V69" t="s" s="19">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="W69" t="s" s="19">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="X69" s="18"/>
       <c r="Y69" s="18"/>
     </row>
     <row r="70" ht="20.35" customHeight="1">
       <c r="A70" t="s" s="30">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="B70" s="31">
         <v>1100000000</v>
@@ -8702,13 +8715,13 @@
         <v>2023</v>
       </c>
       <c r="D70" t="s" s="24">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="E70" t="s" s="24">
         <v>70</v>
       </c>
       <c r="F70" t="s" s="24">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="G70" s="23">
         <v>2023</v>
@@ -8717,7 +8730,7 @@
         <v>2024</v>
       </c>
       <c r="I70" t="s" s="24">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="J70" t="s" s="24">
         <v>99</v>
@@ -8728,7 +8741,7 @@
       <c r="N70" s="25"/>
       <c r="O70" s="26"/>
       <c r="P70" t="s" s="27">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="Q70" t="s" s="27">
         <v>134</v>
@@ -8737,10 +8750,10 @@
       <c r="S70" s="25"/>
       <c r="T70" s="25"/>
       <c r="U70" t="s" s="27">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="V70" t="s" s="27">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="W70" s="26"/>
       <c r="X70" s="26"/>
@@ -8748,7 +8761,7 @@
     </row>
     <row r="71" ht="32.05" customHeight="1">
       <c r="A71" t="s" s="13">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="B71" s="14">
         <v>750000000</v>
@@ -8757,7 +8770,7 @@
         <v>2023</v>
       </c>
       <c r="D71" t="s" s="17">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="E71" t="s" s="17">
         <v>27</v>
@@ -8772,7 +8785,7 @@
         <v>2015</v>
       </c>
       <c r="I71" t="s" s="17">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="J71" t="s" s="17">
         <v>99</v>
@@ -8788,15 +8801,15 @@
         <v>247</v>
       </c>
       <c r="Q71" t="s" s="19">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="R71" s="16"/>
       <c r="S71" s="16"/>
       <c r="T71" t="s" s="19">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="U71" t="s" s="19">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="V71" s="18"/>
       <c r="W71" s="18"/>
@@ -8805,7 +8818,7 @@
     </row>
     <row r="72" ht="32.35" customHeight="1">
       <c r="A72" t="s" s="30">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="B72" s="31">
         <v>730000000</v>
@@ -8814,13 +8827,13 @@
         <v>2023</v>
       </c>
       <c r="D72" t="s" s="24">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="E72" t="s" s="24">
         <v>27</v>
       </c>
       <c r="F72" t="s" s="24">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="G72" s="23">
         <v>2023</v>
@@ -8829,46 +8842,46 @@
         <v>2024</v>
       </c>
       <c r="I72" t="s" s="24">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="J72" t="s" s="24">
         <v>14</v>
       </c>
       <c r="K72" s="25"/>
       <c r="L72" t="s" s="24">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="M72" t="s" s="24">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="N72" t="s" s="24">
         <v>94</v>
       </c>
       <c r="O72" t="s" s="27">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="P72" t="s" s="27">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="Q72" s="26"/>
       <c r="R72" s="25"/>
       <c r="S72" s="25"/>
       <c r="T72" s="25"/>
       <c r="U72" t="s" s="27">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="V72" t="s" s="27">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="W72" t="s" s="27">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="X72" s="26"/>
       <c r="Y72" s="26"/>
     </row>
     <row r="73" ht="20.35" customHeight="1">
       <c r="A73" t="s" s="21">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="B73" s="31">
         <v>577000000</v>
@@ -8884,7 +8897,7 @@
       <c r="G73" s="25"/>
       <c r="H73" s="25"/>
       <c r="I73" t="s" s="24">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="J73" t="s" s="24">
         <v>14</v>
@@ -8894,7 +8907,7 @@
       <c r="M73" s="25"/>
       <c r="N73" s="25"/>
       <c r="O73" t="s" s="27">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="P73" t="s" s="27">
         <v>72</v>
@@ -8906,10 +8919,10 @@
       <c r="S73" s="25"/>
       <c r="T73" s="25"/>
       <c r="U73" t="s" s="27">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="V73" t="s" s="27">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="W73" s="26"/>
       <c r="X73" s="26"/>
@@ -8917,7 +8930,7 @@
     </row>
     <row r="74" ht="32.35" customHeight="1">
       <c r="A74" t="s" s="30">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="B74" s="31">
         <v>426000000</v>
@@ -8926,7 +8939,7 @@
         <v>2023</v>
       </c>
       <c r="D74" t="s" s="24">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="E74" t="s" s="24">
         <v>37</v>
@@ -8951,7 +8964,7 @@
       <c r="M74" s="25"/>
       <c r="N74" s="25"/>
       <c r="O74" t="s" s="27">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="P74" t="s" s="27">
         <v>247</v>
@@ -8961,10 +8974,10 @@
       <c r="S74" s="25"/>
       <c r="T74" s="25"/>
       <c r="U74" t="s" s="27">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="V74" t="s" s="27">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="W74" s="26"/>
       <c r="X74" s="26"/>
@@ -8972,7 +8985,7 @@
     </row>
     <row r="75" ht="44.35" customHeight="1">
       <c r="A75" t="s" s="21">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="B75" s="22">
         <v>421000000</v>
@@ -8981,18 +8994,18 @@
         <v>2023</v>
       </c>
       <c r="D75" t="s" s="24">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="E75" t="s" s="24">
         <v>27</v>
       </c>
       <c r="F75" t="s" s="24">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="G75" s="25"/>
       <c r="H75" s="25"/>
       <c r="I75" t="s" s="24">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="J75" t="s" s="24">
         <v>14</v>
@@ -9002,30 +9015,30 @@
       <c r="M75" s="25"/>
       <c r="N75" s="25"/>
       <c r="O75" t="s" s="27">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="P75" t="s" s="27">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="Q75" s="26"/>
       <c r="R75" s="25"/>
       <c r="S75" s="25"/>
       <c r="T75" s="25"/>
       <c r="U75" t="s" s="27">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="V75" t="s" s="27">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="W75" t="s" s="27">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="X75" s="26"/>
       <c r="Y75" s="26"/>
     </row>
     <row r="76" ht="44.05" customHeight="1">
       <c r="A76" t="s" s="13">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="B76" s="14">
         <v>400000000</v>
@@ -9034,7 +9047,7 @@
         <v>2023</v>
       </c>
       <c r="D76" t="s" s="17">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="E76" t="s" s="17">
         <v>27</v>
@@ -9061,7 +9074,7 @@
       <c r="S76" s="16"/>
       <c r="T76" s="16"/>
       <c r="U76" t="s" s="17">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="V76" s="18"/>
       <c r="W76" s="18"/>
@@ -9070,7 +9083,7 @@
     </row>
     <row r="77" ht="20.35" customHeight="1">
       <c r="A77" t="s" s="21">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="B77" s="22">
         <v>356000000</v>
@@ -9083,12 +9096,12 @@
         <v>27</v>
       </c>
       <c r="F77" t="s" s="24">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="G77" s="25"/>
       <c r="H77" s="25"/>
       <c r="I77" t="s" s="24">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="J77" t="s" s="24">
         <v>14</v>
@@ -9098,30 +9111,30 @@
       <c r="M77" s="25"/>
       <c r="N77" s="25"/>
       <c r="O77" t="s" s="27">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="P77" t="s" s="27">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="Q77" s="26"/>
       <c r="R77" s="25"/>
       <c r="S77" s="25"/>
       <c r="T77" s="25"/>
       <c r="U77" t="s" s="27">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="V77" t="s" s="27">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="W77" t="s" s="27">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="X77" s="26"/>
       <c r="Y77" s="26"/>
     </row>
     <row r="78" ht="32.05" customHeight="1">
       <c r="A78" t="s" s="13">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="B78" s="14">
         <v>293093681</v>
@@ -9130,13 +9143,13 @@
         <v>2023</v>
       </c>
       <c r="D78" t="s" s="17">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="E78" t="s" s="17">
         <v>37</v>
       </c>
       <c r="F78" t="s" s="17">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="G78" s="16"/>
       <c r="H78" s="16"/>
@@ -9148,14 +9161,14 @@
       <c r="N78" s="16"/>
       <c r="O78" s="18"/>
       <c r="P78" t="s" s="19">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="Q78" s="18"/>
       <c r="R78" s="16"/>
       <c r="S78" s="16"/>
       <c r="T78" s="18"/>
       <c r="U78" t="s" s="19">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="V78" s="18"/>
       <c r="W78" s="18"/>
@@ -9164,7 +9177,7 @@
     </row>
     <row r="79" ht="20.35" customHeight="1">
       <c r="A79" t="s" s="30">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="B79" s="31">
         <v>274000000</v>
@@ -9180,7 +9193,7 @@
       <c r="G79" s="25"/>
       <c r="H79" s="25"/>
       <c r="I79" t="s" s="24">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="J79" t="s" s="24">
         <v>14</v>
@@ -9190,7 +9203,7 @@
       <c r="M79" s="25"/>
       <c r="N79" s="25"/>
       <c r="O79" t="s" s="27">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="P79" s="26"/>
       <c r="Q79" s="26"/>
@@ -9198,7 +9211,7 @@
       <c r="S79" s="25"/>
       <c r="T79" s="25"/>
       <c r="U79" t="s" s="27">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="V79" s="26"/>
       <c r="W79" s="26"/>
@@ -9207,7 +9220,7 @@
     </row>
     <row r="80" ht="32.35" customHeight="1">
       <c r="A80" t="s" s="30">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="B80" s="31">
         <v>250000000</v>
@@ -9216,18 +9229,18 @@
         <v>2023</v>
       </c>
       <c r="D80" t="s" s="24">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="E80" t="s" s="24">
         <v>37</v>
       </c>
       <c r="F80" t="s" s="24">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="G80" s="25"/>
       <c r="H80" s="25"/>
       <c r="I80" t="s" s="24">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="J80" t="s" s="24">
         <v>14</v>
@@ -9237,30 +9250,30 @@
       <c r="M80" s="25"/>
       <c r="N80" s="25"/>
       <c r="O80" t="s" s="27">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="P80" t="s" s="27">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="Q80" s="26"/>
       <c r="R80" s="25"/>
       <c r="S80" s="25"/>
       <c r="T80" s="25"/>
       <c r="U80" t="s" s="27">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="V80" t="s" s="27">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="W80" t="s" s="27">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="X80" s="26"/>
       <c r="Y80" s="26"/>
     </row>
     <row r="81" ht="20.35" customHeight="1">
       <c r="A81" t="s" s="30">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="B81" s="31">
         <v>128000000</v>
@@ -9273,12 +9286,12 @@
         <v>37</v>
       </c>
       <c r="F81" t="s" s="24">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="G81" s="25"/>
       <c r="H81" s="25"/>
       <c r="I81" t="s" s="24">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="J81" t="s" s="24">
         <v>14</v>
@@ -9288,7 +9301,7 @@
       <c r="M81" s="25"/>
       <c r="N81" s="25"/>
       <c r="O81" t="s" s="27">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="P81" s="26"/>
       <c r="Q81" s="26"/>
@@ -9296,10 +9309,10 @@
       <c r="S81" s="25"/>
       <c r="T81" s="25"/>
       <c r="U81" t="s" s="27">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="V81" t="s" s="27">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="W81" s="26"/>
       <c r="X81" s="26"/>
@@ -9307,7 +9320,7 @@
     </row>
     <row r="82" ht="68.05" customHeight="1">
       <c r="A82" t="s" s="13">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="B82" s="14">
         <v>80069002</v>
@@ -9316,7 +9329,7 @@
         <v>2023</v>
       </c>
       <c r="D82" t="s" s="17">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="E82" t="s" s="17">
         <v>70</v>
@@ -9349,22 +9362,22 @@
         <v>247</v>
       </c>
       <c r="Q82" t="s" s="19">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="R82" t="s" s="17">
         <v>211</v>
       </c>
       <c r="S82" t="s" s="17">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="T82" t="s" s="17">
         <v>124</v>
       </c>
       <c r="U82" t="s" s="19">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="V82" t="s" s="19">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="W82" s="18"/>
       <c r="X82" s="18"/>
@@ -9372,7 +9385,7 @@
     </row>
     <row r="83" ht="32.05" customHeight="1">
       <c r="A83" t="s" s="13">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="B83" s="14">
         <v>37550000</v>
@@ -9381,7 +9394,7 @@
         <v>2023</v>
       </c>
       <c r="D83" t="s" s="17">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="E83" t="s" s="17">
         <v>70</v>
@@ -9396,7 +9409,7 @@
         <v>2021</v>
       </c>
       <c r="I83" t="s" s="17">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="J83" t="s" s="17">
         <v>99</v>
@@ -9407,14 +9420,14 @@
       <c r="N83" s="16"/>
       <c r="O83" s="18"/>
       <c r="P83" t="s" s="19">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="Q83" s="18"/>
       <c r="R83" s="16"/>
       <c r="S83" s="16"/>
       <c r="T83" s="16"/>
       <c r="U83" t="s" s="19">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="V83" s="18"/>
       <c r="W83" s="18"/>
@@ -9423,7 +9436,7 @@
     </row>
     <row r="84" ht="20.05" customHeight="1">
       <c r="A84" t="s" s="13">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="B84" s="14">
         <v>20000000</v>
@@ -9432,13 +9445,13 @@
         <v>2023</v>
       </c>
       <c r="D84" t="s" s="17">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="E84" t="s" s="17">
         <v>37</v>
       </c>
       <c r="F84" t="s" s="17">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="G84" s="15">
         <v>2023</v>
@@ -9464,7 +9477,7 @@
       <c r="N84" s="16"/>
       <c r="O84" s="18"/>
       <c r="P84" t="s" s="19">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="Q84" t="s" s="19">
         <v>134</v>
@@ -9473,10 +9486,10 @@
       <c r="S84" s="16"/>
       <c r="T84" s="16"/>
       <c r="U84" t="s" s="19">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="V84" t="s" s="19">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="W84" s="16"/>
       <c r="X84" s="18"/>
@@ -9484,7 +9497,7 @@
     </row>
     <row r="85" ht="32.35" customHeight="1">
       <c r="A85" t="s" s="21">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="B85" s="14">
         <v>11320978</v>
@@ -9493,13 +9506,13 @@
         <v>2023</v>
       </c>
       <c r="D85" t="s" s="24">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="E85" t="s" s="24">
         <v>27</v>
       </c>
       <c r="F85" t="s" s="24">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="G85" s="23">
         <v>2017</v>
@@ -9517,27 +9530,27 @@
       <c r="N85" s="25"/>
       <c r="O85" s="26"/>
       <c r="P85" t="s" s="27">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="Q85" s="26"/>
       <c r="R85" s="25"/>
       <c r="S85" s="16"/>
       <c r="T85" s="25"/>
       <c r="U85" t="s" s="27">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="V85" t="s" s="27">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="W85" t="s" s="27">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="X85" s="26"/>
       <c r="Y85" s="26"/>
     </row>
     <row r="86" ht="32.35" customHeight="1">
       <c r="A86" t="s" s="21">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="B86" s="31">
         <v>9000000</v>
@@ -9546,7 +9559,7 @@
         <v>2023</v>
       </c>
       <c r="D86" t="s" s="28">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="E86" t="s" s="24">
         <v>27</v>
@@ -9557,7 +9570,7 @@
       <c r="G86" s="25"/>
       <c r="H86" s="25"/>
       <c r="I86" t="s" s="24">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="J86" t="s" s="24">
         <v>14</v>
@@ -9567,30 +9580,30 @@
       <c r="M86" s="25"/>
       <c r="N86" s="25"/>
       <c r="O86" t="s" s="27">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="P86" t="s" s="27">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="Q86" s="26"/>
       <c r="R86" s="25"/>
       <c r="S86" s="25"/>
       <c r="T86" s="25"/>
       <c r="U86" t="s" s="27">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="V86" t="s" s="27">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="W86" t="s" s="27">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="X86" s="26"/>
       <c r="Y86" s="26"/>
     </row>
     <row r="87" ht="20.35" customHeight="1">
       <c r="A87" t="s" s="21">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="B87" s="22">
         <v>1022000</v>
@@ -9606,7 +9619,7 @@
       <c r="G87" s="25"/>
       <c r="H87" s="25"/>
       <c r="I87" t="s" s="24">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="J87" t="s" s="24">
         <v>14</v>
@@ -9616,7 +9629,7 @@
       <c r="M87" s="25"/>
       <c r="N87" s="25"/>
       <c r="O87" t="s" s="27">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="P87" s="26"/>
       <c r="Q87" s="26"/>
@@ -9624,10 +9637,10 @@
       <c r="S87" s="25"/>
       <c r="T87" s="25"/>
       <c r="U87" t="s" s="27">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="V87" t="s" s="27">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="W87" s="26"/>
       <c r="X87" s="26"/>
@@ -9635,14 +9648,14 @@
     </row>
     <row r="88" ht="32.35" customHeight="1">
       <c r="A88" t="s" s="21">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="B88" s="29"/>
       <c r="C88" s="23">
         <v>2023</v>
       </c>
       <c r="D88" t="s" s="24">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="E88" t="s" s="24">
         <v>27</v>
@@ -9653,7 +9666,7 @@
       <c r="G88" s="25"/>
       <c r="H88" s="25"/>
       <c r="I88" t="s" s="24">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="J88" t="s" s="24">
         <v>102</v>
@@ -9676,14 +9689,14 @@
     </row>
     <row r="89" ht="44.35" customHeight="1">
       <c r="A89" t="s" s="21">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="B89" s="22"/>
       <c r="C89" s="23">
         <v>2023</v>
       </c>
       <c r="D89" t="s" s="24">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="E89" t="s" s="24">
         <v>27</v>
@@ -9698,7 +9711,7 @@
         <v>2023</v>
       </c>
       <c r="I89" t="s" s="24">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="J89" t="s" s="24">
         <v>99</v>
@@ -9709,38 +9722,38 @@
       <c r="N89" s="25"/>
       <c r="O89" s="26"/>
       <c r="P89" t="s" s="27">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="Q89" s="26"/>
       <c r="R89" s="25"/>
       <c r="S89" s="16"/>
       <c r="T89" t="s" s="24">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="U89" t="s" s="27">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="V89" t="s" s="27">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="W89" t="s" s="27">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="X89" t="s" s="27">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="Y89" s="26"/>
     </row>
     <row r="90" ht="32.35" customHeight="1">
       <c r="A90" t="s" s="21">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="B90" s="22"/>
       <c r="C90" s="23">
         <v>2023</v>
       </c>
       <c r="D90" t="s" s="24">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="E90" t="s" s="24">
         <v>27</v>
@@ -9753,7 +9766,7 @@
         <v>2023</v>
       </c>
       <c r="I90" t="s" s="24">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="J90" t="s" s="24">
         <v>99</v>
@@ -9764,19 +9777,19 @@
       <c r="N90" s="25"/>
       <c r="O90" s="26"/>
       <c r="P90" t="s" s="27">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="Q90" s="26"/>
       <c r="R90" s="25"/>
       <c r="S90" s="16"/>
       <c r="T90" t="s" s="24">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="U90" t="s" s="27">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="V90" t="s" s="27">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="W90" s="26"/>
       <c r="X90" s="26"/>
@@ -9784,14 +9797,14 @@
     </row>
     <row r="91" ht="32.35" customHeight="1">
       <c r="A91" t="s" s="21">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="B91" s="22"/>
       <c r="C91" s="23">
         <v>2023</v>
       </c>
       <c r="D91" t="s" s="24">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="E91" t="s" s="24">
         <v>70</v>
@@ -9804,7 +9817,7 @@
         <v>2023</v>
       </c>
       <c r="I91" t="s" s="24">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="J91" t="s" s="24">
         <v>99</v>
@@ -9815,19 +9828,19 @@
       <c r="N91" s="25"/>
       <c r="O91" s="26"/>
       <c r="P91" t="s" s="27">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="Q91" s="26"/>
       <c r="R91" s="25"/>
       <c r="S91" s="16"/>
       <c r="T91" t="s" s="24">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="U91" t="s" s="27">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="V91" t="s" s="27">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="W91" s="26"/>
       <c r="X91" s="26"/>
@@ -9835,14 +9848,14 @@
     </row>
     <row r="92" ht="32.35" customHeight="1">
       <c r="A92" t="s" s="21">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="B92" s="22"/>
       <c r="C92" s="23">
         <v>2023</v>
       </c>
       <c r="D92" t="s" s="24">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="E92" t="s" s="24">
         <v>27</v>
@@ -9853,7 +9866,7 @@
       <c r="G92" s="25"/>
       <c r="H92" s="25"/>
       <c r="I92" t="s" s="24">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="J92" t="s" s="24">
         <v>102</v>
@@ -9869,10 +9882,10 @@
       <c r="S92" s="16"/>
       <c r="T92" s="25"/>
       <c r="U92" t="s" s="27">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="V92" t="s" s="27">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="W92" s="26"/>
       <c r="X92" s="26"/>
@@ -9880,7 +9893,7 @@
     </row>
     <row r="93" ht="32.35" customHeight="1">
       <c r="A93" t="s" s="13">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="B93" s="14">
         <v>3204680640</v>
@@ -9889,7 +9902,7 @@
         <v>2023</v>
       </c>
       <c r="D93" t="s" s="17">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="E93" t="s" s="17">
         <v>27</v>
@@ -9904,7 +9917,7 @@
         <v>2022</v>
       </c>
       <c r="I93" t="s" s="17">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="J93" t="s" s="17">
         <v>99</v>
@@ -9917,27 +9930,27 @@
       <c r="N93" s="25"/>
       <c r="O93" s="26"/>
       <c r="P93" t="s" s="27">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="Q93" s="27"/>
       <c r="R93" s="25"/>
       <c r="S93" s="26"/>
       <c r="T93" s="26"/>
       <c r="U93" t="s" s="24">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="V93" t="s" s="27">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="W93" t="s" s="27">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="X93" s="26"/>
       <c r="Y93" s="26"/>
     </row>
     <row r="94" ht="56.35" customHeight="1">
       <c r="A94" t="s" s="13">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="B94" s="14"/>
       <c r="C94" s="15">
@@ -9957,7 +9970,7 @@
         <v>2021</v>
       </c>
       <c r="I94" t="s" s="17">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="J94" t="s" s="17">
         <v>99</v>
@@ -9973,10 +9986,10 @@
       <c r="S94" s="26"/>
       <c r="T94" s="26"/>
       <c r="U94" t="s" s="24">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="V94" t="s" s="27">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="W94" s="26"/>
       <c r="X94" s="26"/>
@@ -9984,7 +9997,7 @@
     </row>
     <row r="95" ht="32.35" customHeight="1">
       <c r="A95" t="s" s="21">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="B95" s="22">
         <v>45688000000</v>
@@ -9993,7 +10006,7 @@
         <v>2024</v>
       </c>
       <c r="D95" t="s" s="28">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="E95" t="s" s="24">
         <v>27</v>
@@ -10021,7 +10034,7 @@
       <c r="N95" s="25"/>
       <c r="O95" s="26"/>
       <c r="P95" t="s" s="17">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="Q95" t="s" s="27">
         <v>134</v>
@@ -10030,10 +10043,10 @@
       <c r="S95" s="16"/>
       <c r="T95" s="25"/>
       <c r="U95" t="s" s="27">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="V95" t="s" s="27">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="W95" s="26"/>
       <c r="X95" s="26"/>
@@ -10041,7 +10054,7 @@
     </row>
     <row r="96" ht="20.05" customHeight="1">
       <c r="A96" t="s" s="13">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="B96" s="14">
         <v>31000000000</v>
@@ -10050,7 +10063,7 @@
         <v>2024</v>
       </c>
       <c r="D96" t="s" s="17">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="E96" t="s" s="17">
         <v>27</v>
@@ -10065,7 +10078,7 @@
         <v>2021</v>
       </c>
       <c r="I96" t="s" s="17">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="J96" t="s" s="17">
         <v>99</v>
@@ -10078,29 +10091,29 @@
       <c r="N96" s="16"/>
       <c r="O96" s="18"/>
       <c r="P96" t="s" s="19">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="Q96" s="18"/>
       <c r="R96" s="16"/>
       <c r="S96" s="16"/>
       <c r="T96" t="s" s="17">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="U96" t="s" s="19">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="V96" t="s" s="19">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="W96" t="s" s="19">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="X96" s="18"/>
       <c r="Y96" s="18"/>
     </row>
     <row r="97" ht="32.05" customHeight="1">
       <c r="A97" t="s" s="13">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="B97" s="14">
         <v>8000000000</v>
@@ -10109,7 +10122,7 @@
         <v>2024</v>
       </c>
       <c r="D97" t="s" s="17">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="E97" t="s" s="17">
         <v>27</v>
@@ -10131,27 +10144,27 @@
       <c r="N97" s="16"/>
       <c r="O97" s="18"/>
       <c r="P97" t="s" s="19">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="Q97" s="18"/>
       <c r="R97" s="16"/>
       <c r="S97" s="16"/>
       <c r="T97" s="18"/>
       <c r="U97" t="s" s="19">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="V97" t="s" s="19">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="W97" t="s" s="19">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="X97" s="18"/>
       <c r="Y97" s="18"/>
     </row>
     <row r="98" ht="32.35" customHeight="1">
       <c r="A98" t="s" s="21">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="B98" s="22">
         <v>4364000000</v>
@@ -10160,7 +10173,7 @@
         <v>2024</v>
       </c>
       <c r="D98" t="s" s="24">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="E98" t="s" s="24">
         <v>27</v>
@@ -10175,7 +10188,7 @@
         <v>2011</v>
       </c>
       <c r="I98" t="s" s="24">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="J98" t="s" s="24">
         <v>99</v>
@@ -10184,35 +10197,35 @@
         <v>100</v>
       </c>
       <c r="L98" t="s" s="24">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="M98" s="25"/>
       <c r="N98" s="25"/>
       <c r="O98" s="26"/>
       <c r="P98" t="s" s="17">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="Q98" s="26"/>
       <c r="R98" s="25"/>
       <c r="S98" s="16"/>
       <c r="T98" s="25"/>
       <c r="U98" t="s" s="27">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="V98" t="s" s="27">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="W98" t="s" s="27">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="X98" t="s" s="27">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="Y98" s="26"/>
     </row>
     <row r="99" ht="20.05" customHeight="1">
       <c r="A99" t="s" s="13">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="B99" s="14">
         <v>4000000000</v>
@@ -10221,13 +10234,13 @@
         <v>2024</v>
       </c>
       <c r="D99" t="s" s="17">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="E99" t="s" s="17">
         <v>32</v>
       </c>
       <c r="F99" t="s" s="17">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="G99" s="15">
         <v>2012</v>
@@ -10236,7 +10249,7 @@
         <v>2021</v>
       </c>
       <c r="I99" t="s" s="17">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="J99" t="s" s="17">
         <v>99</v>
@@ -10247,14 +10260,14 @@
       <c r="N99" s="16"/>
       <c r="O99" s="18"/>
       <c r="P99" t="s" s="19">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="Q99" s="18"/>
       <c r="R99" s="16"/>
       <c r="S99" s="16"/>
       <c r="T99" s="16"/>
       <c r="U99" t="s" s="19">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="V99" s="18"/>
       <c r="W99" s="18"/>
@@ -10263,7 +10276,7 @@
     </row>
     <row r="100" ht="32.35" customHeight="1">
       <c r="A100" t="s" s="21">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="B100" s="22">
         <v>1700000000</v>
@@ -10272,7 +10285,7 @@
         <v>2024</v>
       </c>
       <c r="D100" t="s" s="24">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="E100" t="s" s="24">
         <v>27</v>
@@ -10287,7 +10300,7 @@
         <v>2024</v>
       </c>
       <c r="I100" t="s" s="24">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="J100" t="s" s="24">
         <v>99</v>
@@ -10305,10 +10318,10 @@
       <c r="S100" s="16"/>
       <c r="T100" s="25"/>
       <c r="U100" t="s" s="27">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="V100" t="s" s="27">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="W100" s="26"/>
       <c r="X100" s="26"/>
@@ -10316,7 +10329,7 @@
     </row>
     <row r="101" ht="44.35" customHeight="1">
       <c r="A101" t="s" s="21">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="B101" s="14">
         <v>1015000000</v>
@@ -10325,7 +10338,7 @@
         <v>2024</v>
       </c>
       <c r="D101" t="s" s="24">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="E101" t="s" s="24">
         <v>27</v>
@@ -10347,33 +10360,33 @@
       <c r="N101" s="25"/>
       <c r="O101" s="26"/>
       <c r="P101" t="s" s="27">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="Q101" t="s" s="27">
         <v>134</v>
       </c>
       <c r="R101" s="25"/>
       <c r="S101" t="s" s="27">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="T101" t="s" s="27">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="U101" t="s" s="27">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="V101" t="s" s="27">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="W101" t="s" s="27">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="X101" s="26"/>
       <c r="Y101" s="26"/>
     </row>
     <row r="102" ht="44.05" customHeight="1">
       <c r="A102" t="s" s="13">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="B102" s="14">
         <v>847807917</v>
@@ -10382,7 +10395,7 @@
         <v>2024</v>
       </c>
       <c r="D102" t="s" s="17">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="E102" s="16"/>
       <c r="F102" s="16"/>
@@ -10401,7 +10414,7 @@
       <c r="S102" s="16"/>
       <c r="T102" s="16"/>
       <c r="U102" t="s" s="19">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="V102" s="18"/>
       <c r="W102" s="18"/>
@@ -10410,7 +10423,7 @@
     </row>
     <row r="103" ht="56.35" customHeight="1">
       <c r="A103" t="s" s="21">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="B103" s="22">
         <v>500000000</v>
@@ -10419,7 +10432,7 @@
         <v>2024</v>
       </c>
       <c r="D103" t="s" s="24">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="E103" t="s" s="24">
         <v>27</v>
@@ -10434,14 +10447,14 @@
         <v>2018</v>
       </c>
       <c r="I103" t="s" s="24">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="J103" t="s" s="24">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="K103" s="25"/>
       <c r="L103" t="s" s="24">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="M103" t="s" s="24">
         <v>102</v>
@@ -10451,10 +10464,10 @@
       </c>
       <c r="O103" s="26"/>
       <c r="P103" t="s" s="27">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="Q103" t="s" s="27">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="R103" t="s" s="24">
         <v>211</v>
@@ -10463,13 +10476,13 @@
         <v>211</v>
       </c>
       <c r="T103" t="s" s="24">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="U103" t="s" s="27">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="V103" t="s" s="27">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="W103" s="26"/>
       <c r="X103" s="26"/>
@@ -10477,7 +10490,7 @@
     </row>
     <row r="104" ht="44.35" customHeight="1">
       <c r="A104" t="s" s="21">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="B104" s="22">
         <v>239000000</v>
@@ -10486,7 +10499,7 @@
         <v>2024</v>
       </c>
       <c r="D104" t="s" s="24">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="E104" t="s" s="24">
         <v>27</v>
@@ -10508,7 +10521,7 @@
       <c r="N104" s="25"/>
       <c r="O104" s="26"/>
       <c r="P104" t="s" s="27">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="Q104" t="s" s="27">
         <v>134</v>
@@ -10517,7 +10530,7 @@
       <c r="S104" s="25"/>
       <c r="T104" s="25"/>
       <c r="U104" t="s" s="27">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="V104" s="26"/>
       <c r="W104" s="26"/>
@@ -10526,7 +10539,7 @@
     </row>
     <row r="105" ht="32.35" customHeight="1">
       <c r="A105" t="s" s="21">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="B105" s="22">
         <v>200000000</v>
@@ -10535,13 +10548,13 @@
         <v>2024</v>
       </c>
       <c r="D105" t="s" s="24">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="E105" t="s" s="24">
         <v>37</v>
       </c>
       <c r="F105" t="s" s="24">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="G105" s="23">
         <v>2019</v>
@@ -10561,16 +10574,16 @@
       <c r="N105" s="25"/>
       <c r="O105" s="26"/>
       <c r="P105" t="s" s="27">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="Q105" s="26"/>
       <c r="R105" s="25"/>
       <c r="S105" s="16"/>
       <c r="T105" t="s" s="24">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="U105" t="s" s="27">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="V105" s="26"/>
       <c r="W105" s="26"/>
@@ -10579,7 +10592,7 @@
     </row>
     <row r="106" ht="32.05" customHeight="1">
       <c r="A106" t="s" s="13">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="B106" s="14">
         <v>190000000</v>
@@ -10588,7 +10601,7 @@
         <v>2024</v>
       </c>
       <c r="D106" t="s" s="17">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="E106" t="s" s="17">
         <v>27</v>
@@ -10599,7 +10612,7 @@
       <c r="G106" s="16"/>
       <c r="H106" s="16"/>
       <c r="I106" t="s" s="17">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="J106" t="s" s="17">
         <v>99</v>
@@ -10617,10 +10630,10 @@
       <c r="S106" s="16"/>
       <c r="T106" s="18"/>
       <c r="U106" t="s" s="19">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="V106" t="s" s="19">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="W106" s="18"/>
       <c r="X106" s="18"/>
@@ -10628,7 +10641,7 @@
     </row>
     <row r="107" ht="32.05" customHeight="1">
       <c r="A107" t="s" s="13">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="B107" s="14">
         <v>176000000</v>
@@ -10637,7 +10650,7 @@
         <v>2024</v>
       </c>
       <c r="D107" t="s" s="17">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="E107" t="s" s="17">
         <v>27</v>
@@ -10673,13 +10686,13 @@
       <c r="R107" s="16"/>
       <c r="S107" s="16"/>
       <c r="T107" t="s" s="17">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="U107" t="s" s="19">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="V107" t="s" s="19">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="W107" s="18"/>
       <c r="X107" s="18"/>
@@ -10687,7 +10700,7 @@
     </row>
     <row r="108" ht="32.35" customHeight="1">
       <c r="A108" t="s" s="21">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="B108" s="14">
         <v>161744998</v>
@@ -10696,7 +10709,7 @@
         <v>2024</v>
       </c>
       <c r="D108" t="s" s="24">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="E108" t="s" s="24">
         <v>27</v>
@@ -10716,7 +10729,7 @@
       <c r="N108" s="25"/>
       <c r="O108" s="26"/>
       <c r="P108" t="s" s="27">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="Q108" t="s" s="27">
         <v>134</v>
@@ -10725,7 +10738,7 @@
       <c r="S108" s="16"/>
       <c r="T108" s="25"/>
       <c r="U108" t="s" s="27">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="V108" s="26"/>
       <c r="W108" s="26"/>
@@ -10734,7 +10747,7 @@
     </row>
     <row r="109" ht="32.35" customHeight="1">
       <c r="A109" t="s" s="21">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="B109" s="22">
         <v>138000000</v>
@@ -10743,7 +10756,7 @@
         <v>2024</v>
       </c>
       <c r="D109" t="s" s="28">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="E109" t="s" s="24">
         <v>27</v>
@@ -10757,13 +10770,13 @@
       </c>
       <c r="I109" s="25"/>
       <c r="J109" t="s" s="24">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="K109" t="s" s="17">
         <v>100</v>
       </c>
       <c r="L109" t="s" s="24">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="M109" s="25"/>
       <c r="N109" s="25"/>
@@ -10776,7 +10789,7 @@
       <c r="S109" s="16"/>
       <c r="T109" s="25"/>
       <c r="U109" t="s" s="27">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="V109" s="26"/>
       <c r="W109" s="26"/>
@@ -10785,7 +10798,7 @@
     </row>
     <row r="110" ht="32.35" customHeight="1">
       <c r="A110" t="s" s="21">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="B110" s="22">
         <v>110840000</v>
@@ -10794,7 +10807,7 @@
         <v>2024</v>
       </c>
       <c r="D110" t="s" s="24">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="E110" t="s" s="24">
         <v>70</v>
@@ -10805,7 +10818,7 @@
       <c r="G110" s="25"/>
       <c r="H110" s="25"/>
       <c r="I110" t="s" s="24">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="J110" t="s" s="24">
         <v>99</v>
@@ -10821,7 +10834,7 @@
       <c r="S110" s="16"/>
       <c r="T110" s="25"/>
       <c r="U110" t="s" s="27">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="V110" s="26"/>
       <c r="W110" s="26"/>
@@ -10830,7 +10843,7 @@
     </row>
     <row r="111" ht="32.05" customHeight="1">
       <c r="A111" t="s" s="13">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="B111" s="14">
         <v>104000000</v>
@@ -10839,7 +10852,7 @@
         <v>2024</v>
       </c>
       <c r="D111" t="s" s="17">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="E111" t="s" s="17">
         <v>27</v>
@@ -10872,10 +10885,10 @@
       <c r="S111" s="16"/>
       <c r="T111" s="16"/>
       <c r="U111" t="s" s="19">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="V111" t="s" s="19">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="W111" s="18"/>
       <c r="X111" s="18"/>
@@ -10883,7 +10896,7 @@
     </row>
     <row r="112" ht="32.35" customHeight="1">
       <c r="A112" t="s" s="21">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="B112" s="22">
         <v>102605250</v>
@@ -10892,7 +10905,7 @@
         <v>2024</v>
       </c>
       <c r="D112" t="s" s="24">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="E112" t="s" s="24">
         <v>37</v>
@@ -10903,7 +10916,7 @@
       <c r="G112" s="25"/>
       <c r="H112" s="25"/>
       <c r="I112" t="s" s="24">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="J112" t="s" s="24">
         <v>102</v>
@@ -10919,10 +10932,10 @@
       <c r="S112" s="16"/>
       <c r="T112" s="25"/>
       <c r="U112" t="s" s="27">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="V112" t="s" s="27">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="W112" s="26"/>
       <c r="X112" s="26"/>
@@ -10930,7 +10943,7 @@
     </row>
     <row r="113" ht="32.35" customHeight="1">
       <c r="A113" t="s" s="21">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="B113" s="22">
         <v>76000000</v>
@@ -10939,7 +10952,7 @@
         <v>2024</v>
       </c>
       <c r="D113" t="s" s="24">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="E113" t="s" s="24">
         <v>27</v>
@@ -10954,14 +10967,14 @@
         <v>2022</v>
       </c>
       <c r="I113" t="s" s="24">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="J113" t="s" s="24">
         <v>99</v>
       </c>
       <c r="K113" s="25"/>
       <c r="L113" t="s" s="24">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="M113" s="25"/>
       <c r="N113" s="25"/>
@@ -10971,13 +10984,13 @@
       <c r="R113" s="25"/>
       <c r="S113" s="16"/>
       <c r="T113" t="s" s="24">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="U113" t="s" s="27">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="V113" t="s" s="27">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="W113" s="26"/>
       <c r="X113" s="26"/>
@@ -10985,7 +10998,7 @@
     </row>
     <row r="114" ht="44.05" customHeight="1">
       <c r="A114" t="s" s="21">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="B114" s="22">
         <v>68000000</v>
@@ -10994,7 +11007,7 @@
         <v>2024</v>
       </c>
       <c r="D114" t="s" s="24">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="E114" t="s" s="24">
         <v>37</v>
@@ -11009,7 +11022,7 @@
         <v>2024</v>
       </c>
       <c r="I114" t="s" s="17">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="J114" t="s" s="24">
         <v>99</v>
@@ -11020,33 +11033,33 @@
       <c r="N114" s="25"/>
       <c r="O114" s="26"/>
       <c r="P114" t="s" s="27">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="Q114" t="s" s="27">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="R114" s="25"/>
       <c r="S114" t="s" s="17">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="T114" s="25"/>
       <c r="U114" t="s" s="27">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="V114" t="s" s="27">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="W114" t="s" s="27">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="X114" t="s" s="27">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="Y114" s="26"/>
     </row>
     <row r="115" ht="32.35" customHeight="1">
       <c r="A115" t="s" s="21">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="B115" s="22">
         <v>53950000</v>
@@ -11055,13 +11068,13 @@
         <v>2024</v>
       </c>
       <c r="D115" t="s" s="24">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="E115" t="s" s="24">
         <v>70</v>
       </c>
       <c r="F115" t="s" s="24">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="G115" s="23">
         <v>2020</v>
@@ -11070,7 +11083,7 @@
         <v>2023</v>
       </c>
       <c r="I115" t="s" s="24">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="J115" t="s" s="24">
         <v>102</v>
@@ -11086,7 +11099,7 @@
       <c r="S115" s="16"/>
       <c r="T115" s="25"/>
       <c r="U115" t="s" s="27">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="V115" s="26"/>
       <c r="W115" s="26"/>
@@ -11095,7 +11108,7 @@
     </row>
     <row r="116" ht="32.35" customHeight="1">
       <c r="A116" t="s" s="21">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="B116" s="22">
         <v>20492785</v>
@@ -11104,7 +11117,7 @@
         <v>2024</v>
       </c>
       <c r="D116" t="s" s="24">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="E116" t="s" s="24">
         <v>37</v>
@@ -11119,7 +11132,7 @@
         <v>2024</v>
       </c>
       <c r="I116" t="s" s="17">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="J116" t="s" s="24">
         <v>99</v>
@@ -11130,31 +11143,31 @@
       <c r="N116" s="25"/>
       <c r="O116" s="26"/>
       <c r="P116" t="s" s="27">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="Q116" s="26"/>
       <c r="R116" s="25"/>
       <c r="S116" s="16"/>
       <c r="T116" s="25"/>
       <c r="U116" t="s" s="27">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="V116" t="s" s="27">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="W116" t="s" s="27">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="X116" t="s" s="27">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="Y116" t="s" s="27">
-        <v>653</v>
+        <v>654</v>
       </c>
     </row>
     <row r="117" ht="20.05" customHeight="1">
       <c r="A117" t="s" s="13">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="B117" s="14">
         <v>10333332</v>
@@ -11163,7 +11176,7 @@
         <v>2024</v>
       </c>
       <c r="D117" t="s" s="17">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="E117" t="s" s="17">
         <v>27</v>
@@ -11178,7 +11191,7 @@
         <v>2024</v>
       </c>
       <c r="I117" t="s" s="17">
-        <v>656</v>
+        <v>657</v>
       </c>
       <c r="J117" t="s" s="17">
         <v>99</v>
@@ -11193,7 +11206,7 @@
       <c r="N117" s="16"/>
       <c r="O117" s="18"/>
       <c r="P117" t="s" s="19">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="Q117" t="s" s="19">
         <v>134</v>
@@ -11202,10 +11215,10 @@
       <c r="S117" s="16"/>
       <c r="T117" s="16"/>
       <c r="U117" t="s" s="19">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="V117" t="s" s="19">
-        <v>659</v>
+        <v>660</v>
       </c>
       <c r="W117" s="18"/>
       <c r="X117" s="18"/>
@@ -11213,7 +11226,7 @@
     </row>
     <row r="118" ht="56.35" customHeight="1">
       <c r="A118" t="s" s="21">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="B118" s="14">
         <v>1729754100</v>
@@ -11222,7 +11235,7 @@
         <v>2025</v>
       </c>
       <c r="D118" t="s" s="24">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="E118" t="s" s="24">
         <v>27</v>
@@ -11242,24 +11255,24 @@
       </c>
       <c r="M118" s="25"/>
       <c r="N118" t="s" s="24">
-        <v>662</v>
+        <v>663</v>
       </c>
       <c r="O118" s="26"/>
       <c r="P118" t="s" s="27">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="Q118" t="s" s="27">
         <v>134</v>
       </c>
       <c r="R118" s="25"/>
       <c r="S118" t="s" s="27">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="T118" t="s" s="27">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="U118" t="s" s="24">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="V118" s="26"/>
       <c r="W118" s="26"/>
@@ -11268,20 +11281,20 @@
     </row>
     <row r="119" ht="56.35" customHeight="1">
       <c r="A119" t="s" s="21">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="B119" s="14"/>
       <c r="C119" s="23">
         <v>2025</v>
       </c>
       <c r="D119" t="s" s="24">
-        <v>666</v>
+        <v>667</v>
       </c>
       <c r="E119" t="s" s="24">
         <v>37</v>
       </c>
       <c r="F119" t="s" s="24">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="G119" s="25"/>
       <c r="H119" s="25"/>
@@ -11301,13 +11314,13 @@
       <c r="R119" s="25"/>
       <c r="S119" s="26"/>
       <c r="T119" t="s" s="27">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="U119" t="s" s="24">
-        <v>668</v>
+        <v>669</v>
       </c>
       <c r="V119" t="s" s="27">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="W119" s="26"/>
       <c r="X119" s="26"/>
@@ -11315,7 +11328,7 @@
     </row>
     <row r="120" ht="44.35" customHeight="1">
       <c r="A120" t="s" s="21">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="B120" s="14">
         <v>75000000</v>
@@ -11324,7 +11337,7 @@
         <v>2025</v>
       </c>
       <c r="D120" t="s" s="24">
-        <v>671</v>
+        <v>672</v>
       </c>
       <c r="E120" t="s" s="24">
         <v>27</v>
@@ -11339,7 +11352,7 @@
         <v>2022</v>
       </c>
       <c r="I120" t="s" s="17">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="J120" t="s" s="24">
         <v>76</v>
@@ -11352,34 +11365,34 @@
       <c r="N120" s="25"/>
       <c r="O120" s="26"/>
       <c r="P120" t="s" s="27">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="Q120" s="27"/>
       <c r="R120" s="25"/>
       <c r="S120" s="26"/>
       <c r="T120" s="26"/>
       <c r="U120" t="s" s="24">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="V120" t="s" s="27">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="W120" t="s" s="27">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="X120" s="26"/>
       <c r="Y120" s="26"/>
     </row>
     <row r="121" ht="56.35" customHeight="1">
       <c r="A121" t="s" s="13">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="B121" s="14"/>
       <c r="C121" s="15">
         <v>2025</v>
       </c>
       <c r="D121" t="s" s="17">
-        <v>678</v>
+        <v>679</v>
       </c>
       <c r="E121" t="s" s="17">
         <v>37</v>
@@ -11411,10 +11424,10 @@
       <c r="R121" s="25"/>
       <c r="S121" s="26"/>
       <c r="T121" t="s" s="27">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="U121" t="s" s="24">
-        <v>679</v>
+        <v>680</v>
       </c>
       <c r="V121" s="26"/>
       <c r="W121" s="26"/>
@@ -11423,7 +11436,7 @@
     </row>
     <row r="122" ht="56.35" customHeight="1">
       <c r="A122" t="s" s="13">
-        <v>680</v>
+        <v>681</v>
       </c>
       <c r="B122" s="14">
         <v>6547000000</v>
@@ -11440,7 +11453,7 @@
         <v>237</v>
       </c>
       <c r="J122" t="s" s="17">
-        <v>681</v>
+        <v>682</v>
       </c>
       <c r="K122" s="16"/>
       <c r="L122" s="16"/>
@@ -11453,20 +11466,20 @@
       <c r="S122" s="26"/>
       <c r="T122" s="26"/>
       <c r="U122" t="s" s="24">
-        <v>682</v>
+        <v>683</v>
       </c>
       <c r="V122" t="s" s="27">
-        <v>683</v>
+        <v>684</v>
       </c>
       <c r="W122" t="s" s="27">
-        <v>684</v>
+        <v>685</v>
       </c>
       <c r="X122" s="26"/>
       <c r="Y122" s="26"/>
     </row>
     <row r="123" ht="44.35" customHeight="1">
       <c r="A123" t="s" s="13">
-        <v>685</v>
+        <v>686</v>
       </c>
       <c r="B123" s="14">
         <v>250000000</v>
@@ -11475,7 +11488,7 @@
         <v>2025</v>
       </c>
       <c r="D123" t="s" s="17">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="E123" t="s" s="17">
         <v>27</v>
@@ -11495,14 +11508,14 @@
       <c r="N123" s="25"/>
       <c r="O123" s="26"/>
       <c r="P123" t="s" s="27">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="Q123" s="27"/>
       <c r="R123" s="25"/>
       <c r="S123" s="26"/>
       <c r="T123" s="26"/>
       <c r="U123" t="s" s="24">
-        <v>688</v>
+        <v>689</v>
       </c>
       <c r="V123" s="26"/>
       <c r="W123" s="26"/>
@@ -11511,7 +11524,7 @@
     </row>
     <row r="124" ht="44.35" customHeight="1">
       <c r="A124" t="s" s="13">
-        <v>689</v>
+        <v>690</v>
       </c>
       <c r="B124" s="14">
         <v>4000000</v>
@@ -11520,7 +11533,7 @@
         <v>2025</v>
       </c>
       <c r="D124" t="s" s="17">
-        <v>690</v>
+        <v>691</v>
       </c>
       <c r="E124" t="s" s="17">
         <v>27</v>
@@ -11549,10 +11562,10 @@
       <c r="S124" s="26"/>
       <c r="T124" s="26"/>
       <c r="U124" t="s" s="24">
-        <v>691</v>
+        <v>692</v>
       </c>
       <c r="V124" t="s" s="27">
-        <v>692</v>
+        <v>693</v>
       </c>
       <c r="W124" s="26"/>
       <c r="X124" s="26"/>
@@ -11560,7 +11573,7 @@
     </row>
     <row r="125" ht="44.35" customHeight="1">
       <c r="A125" t="s" s="13">
-        <v>693</v>
+        <v>694</v>
       </c>
       <c r="B125" s="14">
         <v>16000000</v>
@@ -11569,13 +11582,13 @@
         <v>2025</v>
       </c>
       <c r="D125" t="s" s="17">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="E125" t="s" s="17">
         <v>27</v>
       </c>
       <c r="F125" t="s" s="17">
-        <v>695</v>
+        <v>696</v>
       </c>
       <c r="G125" s="15">
         <v>2024</v>
@@ -11598,7 +11611,7 @@
       <c r="S125" s="26"/>
       <c r="T125" s="26"/>
       <c r="U125" t="s" s="24">
-        <v>696</v>
+        <v>697</v>
       </c>
       <c r="V125" s="26"/>
       <c r="W125" s="26"/>
@@ -11607,7 +11620,7 @@
     </row>
     <row r="126" ht="56.35" customHeight="1">
       <c r="A126" t="s" s="13">
-        <v>697</v>
+        <v>698</v>
       </c>
       <c r="B126" s="14">
         <v>1700000</v>
@@ -11616,13 +11629,13 @@
         <v>2025</v>
       </c>
       <c r="D126" t="s" s="17">
-        <v>698</v>
+        <v>699</v>
       </c>
       <c r="E126" t="s" s="17">
         <v>27</v>
       </c>
       <c r="F126" t="s" s="17">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="G126" s="16"/>
       <c r="H126" s="16"/>
@@ -11641,7 +11654,7 @@
       <c r="S126" s="26"/>
       <c r="T126" s="26"/>
       <c r="U126" t="s" s="24">
-        <v>699</v>
+        <v>700</v>
       </c>
       <c r="V126" s="26"/>
       <c r="W126" s="26"/>
@@ -11650,7 +11663,7 @@
     </row>
     <row r="127" ht="44.35" customHeight="1">
       <c r="A127" t="s" s="13">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="B127" s="14">
         <v>8700018</v>
@@ -11659,7 +11672,7 @@
         <v>2025</v>
       </c>
       <c r="D127" t="s" s="17">
-        <v>701</v>
+        <v>702</v>
       </c>
       <c r="E127" t="s" s="17">
         <v>27</v>
@@ -11677,7 +11690,7 @@
         <v>132</v>
       </c>
       <c r="J127" t="s" s="17">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="K127" s="16"/>
       <c r="L127" s="16"/>
@@ -11690,7 +11703,7 @@
       <c r="S127" s="26"/>
       <c r="T127" s="26"/>
       <c r="U127" t="s" s="24">
-        <v>702</v>
+        <v>703</v>
       </c>
       <c r="V127" s="26"/>
       <c r="W127" s="26"/>
@@ -11699,7 +11712,7 @@
     </row>
     <row r="128" ht="56.35" customHeight="1">
       <c r="A128" t="s" s="13">
-        <v>703</v>
+        <v>704</v>
       </c>
       <c r="B128" s="14">
         <v>18500000</v>
@@ -11708,7 +11721,7 @@
         <v>2025</v>
       </c>
       <c r="D128" t="s" s="17">
-        <v>704</v>
+        <v>705</v>
       </c>
       <c r="E128" t="s" s="17">
         <v>27</v>
@@ -11734,17 +11747,17 @@
       <c r="N128" s="25"/>
       <c r="O128" s="26"/>
       <c r="P128" t="s" s="27">
-        <v>705</v>
+        <v>706</v>
       </c>
       <c r="Q128" s="27"/>
       <c r="R128" s="25"/>
       <c r="S128" s="26"/>
       <c r="T128" s="26"/>
       <c r="U128" t="s" s="24">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="V128" t="s" s="27">
-        <v>707</v>
+        <v>708</v>
       </c>
       <c r="W128" s="26"/>
       <c r="X128" s="26"/>
@@ -11752,7 +11765,7 @@
     </row>
     <row r="129" ht="56.35" customHeight="1">
       <c r="A129" t="s" s="13">
-        <v>708</v>
+        <v>709</v>
       </c>
       <c r="B129" s="14">
         <v>9120775</v>
@@ -11761,7 +11774,7 @@
         <v>2025</v>
       </c>
       <c r="D129" t="s" s="17">
-        <v>709</v>
+        <v>710</v>
       </c>
       <c r="E129" t="s" s="17">
         <v>27</v>
@@ -11787,14 +11800,14 @@
       <c r="N129" s="25"/>
       <c r="O129" s="26"/>
       <c r="P129" t="s" s="27">
-        <v>710</v>
+        <v>711</v>
       </c>
       <c r="Q129" s="27"/>
       <c r="R129" s="25"/>
       <c r="S129" s="26"/>
       <c r="T129" s="26"/>
       <c r="U129" t="s" s="24">
-        <v>711</v>
+        <v>712</v>
       </c>
       <c r="V129" s="26"/>
       <c r="W129" s="26"/>
@@ -11873,167 +11886,168 @@
     <hyperlink ref="V46" r:id="rId60" location="" tooltip="" display="https://www.publimetro.cl/noticias/2022/09/23/100-mil-millones-las-perdidas-de-virginia-reginato-en-municipalidad-de-vina-del-mar/"/>
     <hyperlink ref="W46" r:id="rId61" location="" tooltip="" display="https://www.ciperchile.cl/2024/04/19/vina-del-mar-fiscalia-solicita-a-exalcaldesa-reginato-que-entregue-sus-cartolas-bancarias/"/>
     <hyperlink ref="X46" r:id="rId62" location="" tooltip="" display="https://www.latercera.com/nacional/noticia/vina-del-mar-auditoria-revela-pago-por-23-mil-millones-en-horas-extra-entre-2016-y-2021/5VDK6NYAHRDCBGSIOJW4XFR26M/?outputType=base-amp-type"/>
-    <hyperlink ref="U47" r:id="rId63" location="" tooltip="" display="https://www.meganoticias.cl/nacional/402950-malversacion-10-mil-millones-educacion-sergio-echeverria-exalcalde-san-joaquin-19-01-2023.html"/>
-    <hyperlink ref="U48" r:id="rId64" location="" tooltip="" display="http://www.fiscaliadechile.cl/Fiscalia/sala_prensa/noticias_regional_det.do?id=22739"/>
-    <hyperlink ref="V48" r:id="rId65" location="" tooltip="" display="https://resumen.cl/articulos/exalcalde-pasara-10-anos-en-carcel-por-apropiarse-de-351-millones-de-la-municipalidad-y-de-empresa-electrica"/>
-    <hyperlink ref="U49" r:id="rId66" location="" tooltip="" display="https://radio.uchile.cl/2021/04/16/a-la-carcel-ex-senador-udi-jaime-orpis-es-condenado-a-prision-por-cohecho-y-fraude-al-fisco/"/>
-    <hyperlink ref="U50" r:id="rId67" location="" tooltip="" display="https://www.elciudadano.com/politica/los-18-emblematicos-alcaldes-corruptos-de-la-derecha-historias-de-un-tsunami-delictual/06/22/"/>
-    <hyperlink ref="U51" r:id="rId68" location="" tooltip="" display="https://www.latercera.com/nacional/noticia/formalizan-a-exdirector-general-de-la-pdi-hector-espinosa-fiscalia-le-imputa-apropiacion-de-dineros-de-gastos-reservados-de-la-institucion/IBGS7P3IPVGU3MQU4A7GJDH4UA/"/>
-    <hyperlink ref="V51" r:id="rId69" location="" tooltip="" display="https://www.chvnoticias.cl/exclusivo-chv/todas-las-pruebas-fiscalia-hector-espinosa-pdi_20220828/"/>
-    <hyperlink ref="W51" r:id="rId70" location="" tooltip="" display="https://www.chilevision.cl/noticias/nacional/exdirector-general-de-la-pdi-hector-espinosa-fue-condenado-a-17-anos"/>
-    <hyperlink ref="U52" r:id="rId71" location="" tooltip="" display="https://www.ciperchile.cl/2023/05/26/escandalo-de-cuentas-corrientes-municipales-de-nuble-golpea-en-la-region-metropolitana-contraloria-obliga-a-san-bernardo-a-terminar-contrato/"/>
-    <hyperlink ref="U53" r:id="rId72" location="" tooltip="" display="https://www.latercera.com/earlyaccess/noticia/las-millonarias-transacciones-que-complican-al-alcalde-de-rancagua/GY4SPWLFPJDODKTTXDN7FR74B4/"/>
-    <hyperlink ref="V53" r:id="rId73" location="" tooltip="" display="https://radio.uchile.cl/2023/03/04/tras-allanamiento-a-alcalde-de-rancagua-expertos-en-transparencia-llaman-a-fortalecer-los-mecanismos-para-perseguir-la-corrupcion/"/>
-    <hyperlink ref="W53" r:id="rId74" location="" tooltip="" display="https://www.meganoticias.cl/nacional/442934-alcalde-rancagua-formalizacion-abril-delitos-corrupcion-juan-ramon-godoy-21-03-2024.html"/>
-    <hyperlink ref="X53" r:id="rId75" location="" tooltip="" display="https://www.cde.cl/cde-interpone-querella-criminal-contra-el-alcalde-de-rancagua-por-delitos-asociados-a-hechos-de-corrupcion/"/>
-    <hyperlink ref="U54" r:id="rId76" location="" tooltip="" display="https://radio.uchile.cl/2022/01/19/juzgado-de-pozo-almonte-declara-admisible-querella-contra-alcalde-richard-godoy-por-delitos-tributarios-que-ascenderian-a-mas-de-1300-millones-de-pesos/"/>
-    <hyperlink ref="V54" r:id="rId77" location="" tooltip="" display="https://www.soychile.cl/Iquique/Sociedad/2022/01/19/741037/pozo-querella-richard-godoy-evasion.aspx"/>
-    <hyperlink ref="U55" r:id="rId78" location="" tooltip="" display="https://www.cooperativa.cl/noticias/pais/judicial/denuncias-de-corrupcion/de-que-se-acusa-exactamente-a-daniel-jadue/2024-06-03/202306.html"/>
-    <hyperlink ref="V55" r:id="rId79" location="" tooltip="" display="https://www.cooperativa.cl/noticias/pais/politica/municipales/jadue-sospecha-de-doble-intencionalidad-de-proveedor-que-litiga-contra/2022-02-18/092208.html"/>
-    <hyperlink ref="W55" r:id="rId80" location="" tooltip="" display="https://www.pjud.cl/prensa-y-comunicaciones/noticias-del-poder-judicial/110088"/>
-    <hyperlink ref="U56" r:id="rId81" location="" tooltip="" display="https://www.biobiochile.cl/noticias/nacional/region-de-los-rios/2023/12/10/justicia-admite-querella-contra-alcaldesa-de-rio-bueno-por-malversacion-de-caudales-y-fraude-al-fisco.shtml"/>
-    <hyperlink ref="V56" r:id="rId82" location="" tooltip="" display="https://www.biobiochile.cl/noticias/nacional/region-de-los-rios/2024/10/15/allanan-municipio-de-rio-bueno-en-medio-de-investigacion-por-delitos-de-corrupcion.shtml"/>
-    <hyperlink ref="W56" r:id="rId83" location="" tooltip="" display="https://www.rioenlinea.cl/allanan-municipalidad-de-rio-bueno-por-caso-de-corrupcion-donde-se-investiga-a-alcaldesa-silva-y-exedil-reyes/"/>
-    <hyperlink ref="U57" r:id="rId84" location="" tooltip="" display="https://eltipografo.cl/2022/08/presentan-nueva-querella-por-fraude-al-fisco-contra-ex-alcalde-de-mostazal-sergio-medel-a"/>
-    <hyperlink ref="V57" r:id="rId85" location="" tooltip="" display="https://eltipografo.cl/2023/03/deficit-de-8-mil-millones-en-el-municipio-y-querellas-por-fraude-al-fisco-enfrenta-ex-alcalde-de-mostazal"/>
-    <hyperlink ref="W57" r:id="rId86" location="" tooltip="" display="https://www.biobiochile.cl/noticias/nacional/region-de-ohiggins/2022/08/11/municipio-prepara-querellas-tras-millonarias-irregularidades-en-san-francisco-de-mostazal.shtml"/>
-    <hyperlink ref="U58" r:id="rId87" location="" tooltip="" display="https://cooperativa.cl/noticias/pais/region-de-antofagasta/ex-alcaldesa-karen-rojo-condenada-a-cinco-anos-de-carcel-por-fraude-al/2022-03-24/135330.html"/>
-    <hyperlink ref="V58" r:id="rId88" location="" tooltip="" display="https://cooperativa.cl/noticias/pais/region-de-antofagasta/suprema-rechazo-recurso-de-nulidad-y-karen-rojo-debera-cumplir-pena-en/2022-03-23/155942.html"/>
-    <hyperlink ref="W58" r:id="rId89" location="" tooltip="" display="https://chile.as.com/actualidad/detencion-de-karen-rojo-a-que-partido-pertenecia-cuanto-dinero-robo-y-por-que-estaba-en-holanda-n/"/>
-    <hyperlink ref="U59" r:id="rId90" location="" tooltip="" display="https://www.emol.com/noticias/Nacional/2024/07/10/1136142/suprema-revoca-prision-preventiva.html"/>
-    <hyperlink ref="V59" r:id="rId91" location="" tooltip="" display="https://www.emol.com/noticias/Nacional/2024/06/07/1133101/cronologia-delitos-fiscal-puerto-natales.html"/>
-    <hyperlink ref="U60" r:id="rId92" location="" tooltip="" display="https://www.aduana.cl/megafraude-tributario-investigacion-de-aduanas-fue-clave-para/aduana/2023-12-21/174405.html"/>
-    <hyperlink ref="U61" r:id="rId93" location="" tooltip="" display="https://www.latercera.com/la-tercera-sabado/noticia/cientos-de-depositos-en-efectivo-y-una-cuenta-con-2300-millones-las-pruebas-que-complican-al-tronco-torrealba/LH674LXDYVBR3J5IDIFUCMRIXE/"/>
-    <hyperlink ref="V61" r:id="rId94" location="" tooltip="" display="https://www.ciperchile.cl/2023/05/20/caso-torrealba-detalles-de-gastos-de-campana-de-rn-que-fueron-financiados-con-dineros-de-vitacura/"/>
-    <hyperlink ref="W61" r:id="rId95" location="" tooltip="" display="https://www.elmostrador.cl/noticias/pais/2023/08/08/53-dias-tras-las-rejas-rechazan-solicitud-de-raul-torrealba-y-seguira-en-prision-preventiva/"/>
-    <hyperlink ref="X61" r:id="rId96" location="" tooltip="" display="https://www.latercera.com/nacional/noticia/vitacura-contraloria-objeta-mas-de-4500-millones-a-administracion-de-alcalde-torrealba-en-dos-anos/GK3X6GQBOVB5BFGOV4N52T3PXI/"/>
-    <hyperlink ref="U62" r:id="rId97" location="" tooltip="" display="https://www.latercera.com/nacional/noticia/caso-convenios-ministerio-publico-indaga-traspasos-a-fundaciones-por-mas-de-14-mil-millones-en-ocho-regiones/XUWDKEDIWNDXTOU3RCMSIVQZE4/"/>
-    <hyperlink ref="V62" r:id="rId98" location="" tooltip="" display="https://www.emol.com/noticias/Nacional/2023/07/06/1100220/fundacion-el-desarrollo-de-organizaciones.html"/>
-    <hyperlink ref="V63" r:id="rId99" location="" tooltip="" display="https://www.biobiochile.cl/noticias/nacional/region-de-la-araucania/2024/01/07/imputado-en-arista-caso-convenios-gobernador-de-la-araucania-luciano-rivas-confirma-su-repostulacion.shtml"/>
-    <hyperlink ref="W63" r:id="rId100" location="" tooltip="" display="https://www.cnnchile.com/pais/caso-convenios-fundacion-la-araucania-sueldo_20240901/"/>
-    <hyperlink ref="U64" r:id="rId101" location="" tooltip="" display="https://www.cnnchile.com/pais/destitucion-alcalde-rinconada-contraloria-irregularidades_20230606/"/>
-    <hyperlink ref="V64" r:id="rId102" location="" tooltip="" display="https://munirinconada.cl/alcalde-juan-galdames-se-refiere-a-juicio-de-cuentas-que-ordena-la-restitucion-de-300-millones/"/>
-    <hyperlink ref="U65" r:id="rId103" location="" tooltip="" display="https://www.latercera.com/earlyaccess/noticia/pintar-fachadas-turismo-creativo-y-ayuda-contra-el-suicidio-los-diversos-rubros-de-procultura-la-fundacion-con-mas-convenios-en-la-mira-de-fiscalia/PE7YFQCVMBAOTPHJPTUBEHVPUU/"/>
-    <hyperlink ref="V65" r:id="rId104" location="" tooltip="" display="https://www.ex-ante.cl/perfil-lo-que-hay-que-saber-de-alberto-larrain-sus-vinculos-politicos-y-las-indagaciones-a-la-fundacion-procultura-que-creo/"/>
-    <hyperlink ref="W65" r:id="rId105" location="" tooltip="" display="https://www.emol.com/noticias/Nacional/2024/10/10/1145174/chile-vamos-querella-gore-procultura.html"/>
-    <hyperlink ref="U66" r:id="rId106" location="" tooltip="" display="https://www.malaespinacheck.cl/pais/2023/08/04/fundacion-kimun-el-incumplido-contrato-por-1-200-millones/"/>
-    <hyperlink ref="U67" r:id="rId107" location="" tooltip="" display="https://www.malaespinacheck.cl/pais/2023/08/04/fundacion-kimun-el-incumplido-contrato-por-1-200-millones/"/>
-    <hyperlink ref="U68" r:id="rId108" location="" tooltip="" display="https://www.malaespinacheck.cl/pais/2024/01/03/los-14-detenidos-en-todo-chile-por-el-caso-convenios/"/>
-    <hyperlink ref="V68" r:id="rId109" location="" tooltip="" display="https://www.malaespinacheck.cl/pais/2023/08/04/fundacion-kimun-el-incumplido-contrato-por-1-200-millones/"/>
-    <hyperlink ref="U69" r:id="rId110" location="" tooltip="" display="https://cooperativa.cl/noticias/pais/judicial/denuncias-de-corrupcion/detenido-el-alcalde-de-algarrobo-se-entrego-frente-a-un-motel/2023-11-23/072824.html"/>
-    <hyperlink ref="V69" r:id="rId111" location="" tooltip="" display="https://www.biobiochile.cl/noticias/nacional/region-de-valparaiso/2024/06/04/desfalco-algarrobo-criptomonedas-propiedaes-estados-unidos.shtml"/>
-    <hyperlink ref="W69" r:id="rId112" location="" tooltip="" display="https://www.adnradio.cl/2024/12/05/fiscalia-cierra-investigacion-y-acusa-a-exalcalde-de-algarrobo-de-malversacion-y-lavado-de-activos-pedira-20-anos-de-carcel/"/>
-    <hyperlink ref="U70" r:id="rId113" location="" tooltip="" display="https://www.meganoticias.cl/amp/nacional/442953-mantencion-de-areas-verdes-alcalde-de-arica-firmo-trato-directo-por-1100-millones-con-empresa-creada-14-dias-antes.html"/>
-    <hyperlink ref="V70" r:id="rId114" location="" tooltip="" display="https://conecta2tv.cl/denuncian-ante-la-fiscalia-al-alcalde-de-arica-gerardo-espindola-por-posible-malversacion-de-caudales-publicos/"/>
-    <hyperlink ref="U72" r:id="rId115" location="" tooltip="" display="https://www.latercera.com/nacional/noticia/caso-convenios-ministerio-publico-indaga-traspasos-a-fundaciones-por-mas-de-14-mil-millones-en-ocho-regiones/XUWDKEDIWNDXTOU3RCMSIVQZE4/"/>
-    <hyperlink ref="V72" r:id="rId116" location="" tooltip="" display="https://radio.uchile.cl/2023/11/18/cde-se-querello-contra-fundaciones-en-la-araucania-por-fraude-al-gore/"/>
-    <hyperlink ref="W72" r:id="rId117" location="" tooltip="" display="https://www.cnnchile.com/pais/acusado-desviar-730-millones-mauricio-ojeda-formalizado-corrupcion-caso-convenios_20250101/"/>
-    <hyperlink ref="U73" r:id="rId118" location="" tooltip="" display="https://www.biobiochile.cl/noticias/nacional/region-del-maule/2024/03/11/pdi-allano-gobernacion-del-maule-en-medio-de-investigaciones-por-traspasos-a-urbanismo-social.shtml"/>
-    <hyperlink ref="V73" r:id="rId119" location="" tooltip="" display="https://www.biobiochile.cl/noticias/nacional/region-del-maule/2024/03/12/caso-convenios-jefe-de-control-interno-del-gore-maule-declaro-por-traspasos-a-urbanismo-social.shtml"/>
-    <hyperlink ref="U74" r:id="rId120" location="" tooltip="" display="https://www.latercera.com/nacional/noticia/caso-convenios-ministerio-publico-indaga-traspasos-a-fundaciones-por-mas-de-14-mil-millones-en-ocho-regiones/XUWDKEDIWNDXTOU3RCMSIVQZE4/"/>
-    <hyperlink ref="V74" r:id="rId121" location="" tooltip="" display="https://www.biobiochile.cl/noticias/nacional/region-de-antofagasta/2024/09/03/caso-convenios-formalizan-a-carlos-contreras-por-tres-delitos-de-fraude-al-fisco.shtml"/>
-    <hyperlink ref="U75" r:id="rId122" location="" tooltip="" display="https://radionuevomundo.cl/2023/07/18/gobernador-rivas-suma-al-caso-fundacion-local-traspasos-arbitrarios-a-coihue-y-a-universidades-de-la-araucania/"/>
-    <hyperlink ref="V75" r:id="rId123" location="" tooltip="" display="https://www.elciudadano.com/actualidad/el-entramado-de-ilicitos-de-platas-que-exploto-en-el-gore-araucania-y-que-repercute-en-renovacion-nacional/12/29/"/>
-    <hyperlink ref="W75" r:id="rId124" location="" tooltip="" display="https://resumen.cl/articulos/la-derecha-de-la-araucania-en-el-caso-fundaciones-las-irregularidades-de-espacio-coigue-que-llevaron-al-ministerio-de-justicia-a-solicitar-su-cierre"/>
-    <hyperlink ref="U76" r:id="rId125" location="" tooltip="" display="https://www.elmostrador.cl/dia/2023/03/31/exsubsecretaria-martorell-declaro-como-imputada-por-corrupcion-en-caso-motorola/"/>
-    <hyperlink ref="U77" r:id="rId126" location="" tooltip="" display="https://www.biobiochile.cl/noticias/nacional/region-del-bio-bio/2024/03/13/caso-convenios-allanan-empresa-que-facturo-356-millones-en-convenios-del-gore-bio-bio-y-bonhomia.shtml"/>
-    <hyperlink ref="V77" r:id="rId127" location="" tooltip="" display="https://resumen.cl/articulos/fundacion-contrato-con-dineros-del-gore-biobio-a-empresas-de-coordinador-de-programa-y-a-firma-donde-trabaja-su-hermano-y-su-madre-excandidata-republicana"/>
-    <hyperlink ref="W77" r:id="rId128" location="" tooltip="" display="https://cooperativa.cl/noticias/pais/region-del-biobio/detienen-a-lider-de-empresa-en-allanamiento-por-caso-convenios-pdi/2024-03-13/123002.html"/>
-    <hyperlink ref="U78" r:id="rId129" location="" tooltip="" display="https://www.24horas.cl/actualidad/politica/que-se-le-acusa-a-karina-oliva-emitir-boletas-falsas-defraudar-290-millones"/>
-    <hyperlink ref="U79" r:id="rId130" location="" tooltip="" display="https://www.latercera.com/nacional/noticia/caso-convenios-ministerio-publico-indaga-traspasos-a-fundaciones-por-mas-de-14-mil-millones-en-ocho-regiones/XUWDKEDIWNDXTOU3RCMSIVQZE4/"/>
-    <hyperlink ref="U80" r:id="rId131" location="" tooltip="" display="https://radio.uchile.cl/2023/11/28/755094/"/>
-    <hyperlink ref="V80" r:id="rId132" location="" tooltip="" display="https://elpais.com/chile/2023-08-05/caso-lenceria-la-telenovelesca-arista-de-la-trama-de-corrupcion-que-hace-temblar-la-politica-chilena.html"/>
-    <hyperlink ref="W80" r:id="rId133" location="" tooltip="" display="https://www.malaespinacheck.cl/pais/2024/01/03/los-14-detenidos-en-todo-chile-por-el-caso-convenios/"/>
-    <hyperlink ref="U81" r:id="rId134" location="" tooltip="" display="https://www.latercera.com/nacional/noticia/caso-convenios-ministerio-publico-indaga-traspasos-a-fundaciones-por-mas-de-14-mil-millones-en-ocho-regiones/XUWDKEDIWNDXTOU3RCMSIVQZE4/"/>
-    <hyperlink ref="V81" r:id="rId135" location="" tooltip="" display="https://www.meganoticias.cl/nacional/420687-nexos-politicos-gore-arica-fundacion-comprometidos-280-millones-25-7-2023.html"/>
-    <hyperlink ref="U82" r:id="rId136" location="" tooltip="" display="https://www.diarioconstitucional.cl/2023/06/20/ex-administrador-municipal-que-aprobo-el-financiamiento-para-que-alcalde-concejales-y-funcionarios-publicos-de-tierra-amarilla-emprendieran-viaje-turistico-a-la-habana-y-varadero-incurre-en-el-delit/"/>
-    <hyperlink ref="U83" r:id="rId137" location="" tooltip="" display="https://www.diarioviregion.cl/index.php/noticias/27551-ex-alcalde-de-san-fernando-juan-paulo-molina-condenado-por-fraude-al-fisco-reiterado"/>
-    <hyperlink ref="U84" r:id="rId138" location="" tooltip="" display="https://www.emol.com/noticias/Nacional/2023/11/15/1112897/daniel-jadue-declaracion-farmacias-populares.html"/>
-    <hyperlink ref="V84" r:id="rId139" location="" tooltip="" display="https://www.biobiochile.cl/noticias/nacional/chile/2024/04/02/fiscalia-formalizara-a-daniel-jadue-por-cohecho-administracion-desleal-fraude-al-fisco-y-estafa.shtml"/>
-    <hyperlink ref="U85" r:id="rId140" location="" tooltip="" display="https://www.elciudadano.com/reportaje-investigacion/fue-funcionario-de-confianza-de-felipe-alessandri-fiscalia-investiga-a-diputado-republicano-agustin-romero-por-fraude-al-fisco/03/07/"/>
-    <hyperlink ref="V85" r:id="rId141" location="" tooltip="" display="https://www.cooperativa.cl/noticias/pais/judicial/justicia-designo-a-ministra-de-fuero-para-cobrar-pago-de-horas-extras-a/2023-11-27/155546.html"/>
-    <hyperlink ref="W85" r:id="rId142" location="" tooltip="" display="https://interferencia.cl/articulos/corte-designa-ministra-de-fuero-para-cobrar-11-millones-que-diputado-republicano-recibio"/>
-    <hyperlink ref="U86" r:id="rId143" location="" tooltip="" display="https://www.malaespinacheck.cl/pais/2024/01/03/los-14-detenidos-en-todo-chile-por-el-caso-convenios/"/>
-    <hyperlink ref="V86" r:id="rId144" location="" tooltip="" display="https://www.elciudadano.com/actualidad/el-entramado-de-ilicitos-de-platas-que-exploto-en-el-gore-araucania-y-que-repercute-en-renovacion-nacional/12/29/"/>
-    <hyperlink ref="W86" r:id="rId145" location="" tooltip="" display="https://elperiodico.cl/contraloria-corrobora-participacion-de-exfuncionaria-del-gore-araucania-en-comision-que-aprobo-proyecto-de-fundacion-que-posteriormente-la-contrato/"/>
-    <hyperlink ref="U87" r:id="rId146" location="" tooltip="" display="https://www.emol.com/noticias/Nacional/2024/02/20/1122268/contraloria-caso-convenios-minvu-serviu.html"/>
-    <hyperlink ref="V87" r:id="rId147" location="" tooltip="" display="https://www.ex-ante.cl/confidencial-las-47-fundaciones-indagadas-por-justicia-en-el-caso-convenios/"/>
-    <hyperlink ref="W89" r:id="rId148" location="" tooltip="" display="https://www.biobiochile.cl/noticias/nacional/region-de-nuble/2023/10/15/cuentas-corrientes-tesorero-municipal-acusado-de-cohecho-logra-salida-alternativa-tras-donar-200-mil.shtml"/>
-    <hyperlink ref="X89" r:id="rId149" location="" tooltip="" display="https://www.biobiochile.cl/noticias/nacional/region-de-nuble/2023/04/25/causa-por-corrupcion-mantienen-prision-preventiva-para-alcalde-de-san-ignacio-y-un-operador-politico.shtml"/>
-    <hyperlink ref="V90" r:id="rId150" location="" tooltip="" display="https://www.emol.com/noticias/Nacional/2024/02/15/1121826/caso-cuentas-corrientes.html"/>
-    <hyperlink ref="U91" r:id="rId151" location="" tooltip="" display="https://www.emol.com/noticias/Nacional/2024/02/15/1121826/caso-cuentas-corrientes.html"/>
-    <hyperlink ref="V91" r:id="rId152" location="" tooltip="" display="https://radio.uchile.cl/2024/02/13/caso-cuentas-corrientes-detienen-a-alcalde-de-bulnes-por-delitos-economicos/"/>
-    <hyperlink ref="U92" r:id="rId153" location="" tooltip="" display="https://www.biobiochile.cl/noticias/nacional/region-de-nuble/2023/04/19/ex-udi-y-exasesor-de-sauerbaum-quien-es-el-operador-politico-investigado-por-corrupcion-en-nuble.shtml"/>
-    <hyperlink ref="V92" r:id="rId154" location="" tooltip="" display="https://www.biobiochile.cl/noticias/nacional/region-de-nuble/2023/04/25/causa-por-corrupcion-mantienen-prision-preventiva-para-alcalde-de-san-ignacio-y-un-operador-politico.shtml"/>
-    <hyperlink ref="U93" r:id="rId155" location="" tooltip="" display="https://www.t13.cl/noticia/politica/exclusivo-t13-millonario-pago-horas-extra-municipalidad-vitacura"/>
-    <hyperlink ref="V93" r:id="rId156" location="" tooltip="" display="https://www.latercera.com/la-tercera-pm/noticia/caso-torrealba-excontador-de-vitacura-apunta-a-que-platas-politicas-se-justificaban-bajo-el-rotulo-horas-extra/4XN3AQ3ZWNA4NHJZ23ZWE22DJI/"/>
-    <hyperlink ref="W93" r:id="rId157" location="" tooltip="" display="https://vergara240.udp.cl/municipalidad-las-condes-providencia-vitacura-horas-extraordinarias/"/>
-    <hyperlink ref="U94" r:id="rId158" location="" tooltip="" display="https://www.adnradio.cl/2025/05/08/operaban-desde-la-gestion-de-barriga-detienen-a-funcionarios-de-maipu-por-presunta-red-de-corrupcion-en-licencias-de-conducir/"/>
-    <hyperlink ref="V94" r:id="rId159" location="" tooltip="" display="https://www.elciudadano.com/chile/detienen-a-funcionarios-de-la-municipalidad-de-maipu-por-presunta-red-de-corrupcion-que-operaba-desde-gestion-de-barriga/05/08/"/>
-    <hyperlink ref="U95" r:id="rId160" location="" tooltip="" display="https://www.elmostrador.cl/noticias/pais/2024/12/27/auditoria-a-la-caja-pagadora-de-las-condes-45-mil-millones-en-horas-extras-y-25-causas-laborales/"/>
-    <hyperlink ref="V95" r:id="rId161" location="" tooltip="" display="https://www.cnnchile.com/pais/45-mil-millones-en-horas-extras-las-condes-concluye-auditoria-externa-y-apunta-a-revisar-corporaciones-municipales_20241227/"/>
-    <hyperlink ref="U96" r:id="rId162" location="" tooltip="" display="https://radio.uchile.cl/2024/01/17/en-suspenso-prision-preventiva-para-cathy-barriga-tribunal-dictara-cautelar-este-jueves/"/>
-    <hyperlink ref="V96" r:id="rId163" location="" tooltip="" display="https://lavozdemaipu.cl/cathy-barriga-ultimo-informe-con-peras-y-manzanas/"/>
-    <hyperlink ref="W96" r:id="rId164" location="" tooltip="" display="https://www.cooperativa.cl/noticias/pais/judicial/denuncias-de-corrupcion/cathy-barriga-quedo-en-prision-preventiva/2024-11-12/174907.html"/>
-    <hyperlink ref="U97" r:id="rId165" location="" tooltip="" display="https://www.latercera.com/la-tercera-pm/noticia/estafa-fraude-y-falsificacion-el-avance-en-la-investigacion-penal-en-las-condes-que-remece-a-la-administracion-penaloza/X7ZBPJAYLRA47LINUR5COTA5HY/"/>
-    <hyperlink ref="V97" r:id="rId166" location="" tooltip="" display="https://www.latercera.com/nacional/noticia/las-investigaciones-que-envuelven-al-municipio-de-las-condes-y-a-su-alcaldesa-daniela-penaloza/GYYWEXRFXNGJVKFJPOEWRQUB7I/"/>
-    <hyperlink ref="W97" r:id="rId167" location="" tooltip="" display="https://www.latercera.com/nacional/noticia/contraloria-sanciona-a-exalcaldesa-penaloza-por-compra-de-cesfam-en-las-condes-y-destituye-al-exdirector-de-control/"/>
-    <hyperlink ref="U98" r:id="rId168" location="" tooltip="" display="https://www.elmostrador.cl/noticias/pais/2024/12/12/el-ultimo-coletazo-del-caso-basura-exalcalde-luis-plaza-rn-condenado-por-fraude-al-fisco/"/>
-    <hyperlink ref="V98" r:id="rId169" location="" tooltip="" display="https://www.ciperchile.cl/2015/05/15/las-evidencias-contra-los-alcaldes-vittori-dc-y-plaza-rn-por-millonarios-negocios-irregulares-en-maipu-y-cerro-navia/"/>
-    <hyperlink ref="W98" r:id="rId170" location="" tooltip="" display="https://www.latercera.com/nacional/noticia/a-13-anos-de-que-se-iniciara-el-caso-condenan-a-exalcalde-luis-plaza-rn-por-fraude-al-fisco-en-ultima-arista-del-emblematico-caso-basura/TGWT6RCHCJHEBP5MVQXK2VL2AE/"/>
-    <hyperlink ref="X98" r:id="rId171" location="" tooltip="" display="https://www.adnradio.cl/2025/06/03/por-fraude-al-fisco-reiterado-en-caso-basura-exalcalde-luis-plaza-es-condenado-a-tres-anos-de-presidio-con-el-beneficio-de-libertad-vigilada/"/>
-    <hyperlink ref="U99" r:id="rId172" location="" tooltip="" display="https://www.elrancaguino.cl/2024/01/18/hasta-35-anos-de-carcel-y-el-pago-de-2-mil-millones-de-pesos-en-multas-arriesga-el-ex-alcalde-san-fernando-luis-berwart/"/>
-    <hyperlink ref="U100" r:id="rId173" location="" tooltip="" display="https://www.elcomunal.cl/comunales/2024/03/25/15-demandas-1-querella-y-17-solicitudes-de-arresto-por-deudas-de-1500-millones-del-municipio-de-la-higuera-sacuden-a-yerko-galleguillos/"/>
-    <hyperlink ref="V100" r:id="rId174" location="" tooltip="" display="https://www.elcomunal.cl/comunales/2024/10/04/contraloria-detecta-graves-irregularidades-en-municipalidad-de-la-higuera-y-envia-antecedentes-a-fiscalia/"/>
-    <hyperlink ref="U101" r:id="rId175" location="" tooltip="" display="https://www.biobiochile.cl/noticias/economia/actualidad-economica/2024/08/12/caso-audio-sii-se-querella-contra-luis-hermosilla-y-maria-villalobos-por-delitos-tributarios.shtml"/>
-    <hyperlink ref="V101" r:id="rId176" location="" tooltip="" display="https://www.publimetro.cl/noticias/2024/08/12/caso-audios-sii-se-querella-contra-luis-hermosilla-y-fernanda-villalobos-por-delitos-tributarios-y-fiscalia-solicita-formalizacion/"/>
-    <hyperlink ref="W101" r:id="rId177" location="" tooltip="" display="https://www.t13.cl/noticia/politica/caso-audios-las-pruebas-revelaciones-fiscalia-formalizacion-hermosilla-villalob-21-8-2024"/>
-    <hyperlink ref="U102" r:id="rId178" location="" tooltip="" display="https://www.biobiochile.cl/noticias/nacional/chile/2024/03/19/milicogate-dictan-procesamiento-contra-general-y-coroneles-r-por-presunto-fraude-de-519-millones.shtml"/>
-    <hyperlink ref="U103" r:id="rId179" location="" tooltip="" display="https://www.latercera.com/campuslt/noticia/luminarias-juzgado-de-garantia-de-iquique-condena-a-exconcejal-felipe-arenas-por-fraude-al-fisco-y-cohecho/OR3BBHZLARCULI7J5A22A66CSU/"/>
-    <hyperlink ref="V103" r:id="rId180" location="" tooltip="" display="https://iquiquetv.cl/2024/07/02/caso-luminarias-led-condenan-a-ex-concejal-felipe-arenas-por-cohecho-y-fraude-al-fisco/"/>
-    <hyperlink ref="U104" r:id="rId181" location="" tooltip="" display="https://www.latercera.com/opinion/noticia/columna-de-daniel-matamala-cual-elefante/EOAKP2PXWJHSFDBAKRXGVVS5ZA/"/>
-    <hyperlink ref="U105" r:id="rId182" location="" tooltip="" display="https://www.latercera.com/nacional/noticia/mas-de-200-millones-para-sanar-deudas-de-achifarp-y-pagos-a-funcionarios-fantasma-los-hitos-que-marcaron-el-primer-dia-de-formalizacion-del-alcalde-de-recoleta/YGFDCRRVJNFSXAA7KWM3YEIIUQ/"/>
-    <hyperlink ref="U106" r:id="rId183" location="" tooltip="" display="https://www.malaespinacheck.cl/pais/2024/01/29/quien-es-daniel-agusto-perez-el-exalcalde-formalizado-por-fraude-al-fisco/"/>
-    <hyperlink ref="V106" r:id="rId184" location="" tooltip="" display="https://www.biobiochile.cl/noticias/nacional/region-de-antofagasta/2024/01/24/son-11-casos-de-karen-rojo-formalizaron-a-exdelegado-de-pinera-en-antofagasta-por-fraude-al-fisco.shtml"/>
-    <hyperlink ref="U107" r:id="rId185" location="" tooltip="" display="https://www.latercera.com/nacional/noticia/exalcalde-de-nunoa-andres-zarhi-queda-con-arresto-domiciliario-nocturno-tras-formalizacion-por-fraude-al-fisco/64LJ53FVUJA4BIGCC4DMKIJWRU/"/>
-    <hyperlink ref="V107" r:id="rId186" location="" tooltip="" display="https://www.emol.com/noticias/Nacional/2024/02/27/1123065/decretan-arresto-domiciliario-nocturno-andreszarhi.html"/>
-    <hyperlink ref="U108" r:id="rId187" location="" tooltip="" display="https://www.biobiochile.cl/noticias/economia/actualidad-economica/2024/10/11/sii-se-querello-contra-los-hermanos-jalaff-por-facturas-falsas-y-provocar-dano-fiscal-por-161-744-998.shtml"/>
-    <hyperlink ref="U109" r:id="rId188" location="" tooltip="" display="https://www.meganoticias.cl/nacional/470071-cde-querella-exjefe-gobierno-digital-pinera-fraude-fisco-mega-investiga-17-12-2024.html"/>
-    <hyperlink ref="U110" r:id="rId189" location="" tooltip="" display="https://www.biobiochile.cl/noticias/nacional/region-de-la-araucania/2024/01/25/caso-cuentas-corrientes-contraloria-ordena-al-municipio-de-lautaro-restituir-cerca-de-80-millones.shtml"/>
-    <hyperlink ref="U111" r:id="rId190" location="" tooltip="" display="https://www.theclinic.cl/2024/02/27/pdi-acorrala-al-circulo-de-virginia-reginato-udi-acusa-a-exadministrador-municipal-de-millonarios-gastos-en-restaurantes-y-licorerias/"/>
-    <hyperlink ref="V111" r:id="rId191" location="" tooltip="" display="https://www.soychile.cl/valparaiso/sociedad/2024/01/22/844669/formalizacion-vina-boisier-fisco-reacciones.html"/>
-    <hyperlink ref="U112" r:id="rId192" location="" tooltip="" display="https://www.latercera.com/nacional/noticia/contraloria-detecta-dos-nuevos-municipios-involucrados-en-el-caso-cuentas-corrientes-y-deriva-antecedentes-a-la-fiscalia/5C3ZRUU3WFF4BFYSN4BG4GD7QE/"/>
-    <hyperlink ref="V112" r:id="rId193" location="" tooltip="" display="https://www.elsancarlino.cl/2024/06/contraloria-detecta-dos-nuevos.html"/>
-    <hyperlink ref="U113" r:id="rId194" location="" tooltip="" display="https://www.biobiochile.cl/noticias/nacional/region-de-los-rios/2024/02/15/cuentas-corrientes-rio-bueno-debera-restituir-76-millones-por-pagos-improcedentes-a-gestion-global.shtml"/>
-    <hyperlink ref="V113" r:id="rId195" location="" tooltip="" display="https://www.biobiochile.cl/noticias/nacional/region-de-los-rios/2023/09/24/caso-cuentas-corrientes-exalcalde-de-rio-bueno-declara-en-fiscalia-por-contratacion-de-gestion-global.shtml"/>
-    <hyperlink ref="U114" r:id="rId196" location="" tooltip="" display="https://www.canal9.cl/episodios/noticias/2024/07/26/alcalde-de-coronel-y-concejal-araya-seran-formalizados-por-caso-puerto-coronel"/>
-    <hyperlink ref="V114" r:id="rId197" location="" tooltip="" display="https://www.cooperativa.cl/noticias/pais/region-del-biobio/formalizaran-por-delitos-de-corrupcion-al-alcalde-de-coronel-y-a-otras/2024-07-26/084551.html"/>
-    <hyperlink ref="W114" r:id="rId198" location="" tooltip="" display="https://www.meganoticias.cl/nacional/459252-querella-alcalde-coronel-boris-chamorro-cohecho-pago-coimas-17-09-2024.html"/>
-    <hyperlink ref="X114" r:id="rId199" location="" tooltip="" display="https://eldesconcierto.cl/2024/12/16/arresto-domiciliario-nocturno-para-alcalde-electo-de-coronel-es-imputado-por-delitos-de-corrupcion?utm_term=Autofeed&amp;utm_medium=Social&amp;utm_source=Twitter#Echobox=1734388166"/>
-    <hyperlink ref="U115" r:id="rId200" location="" tooltip="" display="https://www.latercera.com/nacional/noticia/contraloria-detecta-dos-nuevos-municipios-involucrados-en-el-caso-cuentas-corrientes-y-deriva-antecedentes-a-la-fiscalia/5C3ZRUU3WFF4BFYSN4BG4GD7QE/"/>
-    <hyperlink ref="U116" r:id="rId201" location="" tooltip="" display="https://www.biobiochile.cl/noticias/nacional/region-de-los-lagos/2023/09/13/causa-por-corrupcion-y-lavado-de-activos-fiscal-explica-allanamiento-en-municipio-de-puerto-montt.shtml"/>
-    <hyperlink ref="V116" r:id="rId202" location="" tooltip="" display="https://www.diariodepuertomontt.cl/noticia/politica/2024/08/ter-ordena-la-remocion-del-alcalde-de-puerto-montt"/>
-    <hyperlink ref="W116" r:id="rId203" location="" tooltip="" display="https://www.emol.com/noticias/Nacional/2024/08/23/1140650/remueven-alcalde-de-puerto-montt.html"/>
-    <hyperlink ref="X116" r:id="rId204" location="" tooltip="" display="https://www.24horas.cl/regiones/zona-sur/los-lagos/alcalde-de-puerto-montt-destituido-notable-abandono-deberes"/>
-    <hyperlink ref="Y116" r:id="rId205" location="" tooltip="" display="https://www.biobiochile.cl/noticias/nacional/region-de-los-lagos/2024/10/23/exalcalde-de-puerto-montt-gervoy-paredes-queda-en-prision-preventiva-por-delitos-de-corrupcion.shtml"/>
-    <hyperlink ref="U119" r:id="rId206" location="" tooltip="" display="https://www.latercera.com/nacional/noticia/hassler-libre-de-cargos-cooper-cierra-investigacion-por-fallida-compra-de-clinica-sierra-bella-y-dice-que-no-hay-delito/"/>
-    <hyperlink ref="V119" r:id="rId207" location="" tooltip="" display="https://www.t13.cl/noticia/politica/alerta-teletrece-fiscal-cooper-decide-no-perseverar-investigacion-sierra-bella-26-5-2025?utm_source=Facebook&amp;utm_medium=Stack&amp;utm_campaign=Share13&amp;utm_id=share13"/>
-    <hyperlink ref="U120" r:id="rId208" location="" tooltip="" display="https://www.latercera.com/nacional/noticia/cde-se-querella-contra-el-diputado-joaquin-lavin-por-malversacion-de-caudales-publicos/"/>
-    <hyperlink ref="V120" r:id="rId209" location="" tooltip="" display="https://www.cnnchile.com/pais/30-facturas-22-millones-querella-cde-joaquin-lavin-leon_20250531/"/>
-    <hyperlink ref="W120" r:id="rId210" location="" tooltip="" display="https://www.biobiochile.cl/especial/bbcl-investiga/noticias/articulos/2025/05/30/facturas-falsas-en-el-congreso-cde-sale-a-la-caza-de-lavin-jr-y-su-circulo-de-hierro.shtml"/>
-    <hyperlink ref="U121" r:id="rId211" location="" tooltip="" display="https://www.biobiochile.cl/especial/bbcl-investiga/noticias/articulos/2025/03/21/libre-de-responsabilidad-carolina-toha-es-absuelta-en-dos-juicios-de-cuentas-por-irregularidades.shtml"/>
-    <hyperlink ref="U122" r:id="rId212" location="" tooltip="" display="https://www.biobiochile.cl/especial/bbcl-investiga/noticias/articulos/2025/03/28/fraude-en-gore-metropolitano-funcionario-acepto-facturas-falsas-de-empresa-por-mas-de-6-500-millones.shtml"/>
-    <hyperlink ref="V122" r:id="rId213" location="" tooltip="" display="https://www.latercera.com/pulso-pm/noticia/xepelin-se-querella-por-millonaria-estafa-con-facturas-falsas-vinculadas-al-gore-metropolitano/"/>
-    <hyperlink ref="W122" r:id="rId214" location="" tooltip="" display="https://www.elagora.net/millonario-fraude-en-gore-metropolitano/"/>
-    <hyperlink ref="U123" r:id="rId215" location="" tooltip="" display="https://contrapoderchile.cl/interponen-querella-criminal-en-contra-de-alcalde-sebastian-sichel-por-falsificacion-de-instrumento-publico/"/>
-    <hyperlink ref="U124" r:id="rId216" location="" tooltip="" display="https://reportea.cl/2025/11/29/los-secretos-politicos-de-yaber-arriendos-para-dos-parlamentarios-y-un-cheque-para-el-senador-gahona/"/>
-    <hyperlink ref="V124" r:id="rId217" location="" tooltip="" display="https://www.ciperchile.cl/2025/11/27/hija-de-senador-gahona-fue-contratada-por-sergio-yaber-en-el-cbr-de-puente-alto/"/>
-    <hyperlink ref="U125" r:id="rId218" location="" tooltip="" display="https://reportea.cl/2025/11/22/trama-bielorrusa-documento-del-bci-revela-pago-de-16-millones-de-sergio-yaber-al-senador-walker/"/>
-    <hyperlink ref="U126" r:id="rId219" location="" tooltip="" display="https://www.ciperchile.cl/2025/11/19/arista-bielorrusa-en-un-dialogo-pinchado-por-el-os7-el-conservador-yaber-dijo-que-le-entrego-17-millones-a-diputado-republicano/"/>
-    <hyperlink ref="U127" r:id="rId220" location="" tooltip="" display="https://contrapoderchile.cl/concejala-de-la-florida-rn-fue-contratada-en-el-municipio-de-santiago-y-ha-recibido-mas-de-8-millones-en-horas-extras/"/>
-    <hyperlink ref="U128" r:id="rId221" location="" tooltip="" display="https://www.adnradio.cl/2025/12/19/golpe-a-la-gestion-carter-contraloria-pide-devolver-fondos-pagados-a-cecilia-perez-su-exmarido-y-su-cunada-en-la-florida/"/>
-    <hyperlink ref="V128" r:id="rId222" location="" tooltip="" display="https://www.ciperchile.cl/2025/12/19/contraloria-revisa-trabajo-de-cecilia-perez-en-la-florida-solicita-devolucion-de-18-millones-por-labores-no-acreditadas/"/>
-    <hyperlink ref="U129" r:id="rId223" location="" tooltip="" display="https://contrapoderchile.cl/contraloria-confirma-que-francisco-orrego-devolvio-9-millones-a-la-municipalidad-de-la-florida-por-contratacion-irregular/"/>
+    <hyperlink ref="Y46" r:id="rId63" location="" tooltip="" display="https://contrapoderchile.cl/fiscalia-confirma-que-virginia-reginato-udi-esta-en-calidad-de-imputada-por-fraude-al-fisco/"/>
+    <hyperlink ref="U47" r:id="rId64" location="" tooltip="" display="https://www.meganoticias.cl/nacional/402950-malversacion-10-mil-millones-educacion-sergio-echeverria-exalcalde-san-joaquin-19-01-2023.html"/>
+    <hyperlink ref="U48" r:id="rId65" location="" tooltip="" display="http://www.fiscaliadechile.cl/Fiscalia/sala_prensa/noticias_regional_det.do?id=22739"/>
+    <hyperlink ref="V48" r:id="rId66" location="" tooltip="" display="https://resumen.cl/articulos/exalcalde-pasara-10-anos-en-carcel-por-apropiarse-de-351-millones-de-la-municipalidad-y-de-empresa-electrica"/>
+    <hyperlink ref="U49" r:id="rId67" location="" tooltip="" display="https://radio.uchile.cl/2021/04/16/a-la-carcel-ex-senador-udi-jaime-orpis-es-condenado-a-prision-por-cohecho-y-fraude-al-fisco/"/>
+    <hyperlink ref="U50" r:id="rId68" location="" tooltip="" display="https://www.elciudadano.com/politica/los-18-emblematicos-alcaldes-corruptos-de-la-derecha-historias-de-un-tsunami-delictual/06/22/"/>
+    <hyperlink ref="U51" r:id="rId69" location="" tooltip="" display="https://www.latercera.com/nacional/noticia/formalizan-a-exdirector-general-de-la-pdi-hector-espinosa-fiscalia-le-imputa-apropiacion-de-dineros-de-gastos-reservados-de-la-institucion/IBGS7P3IPVGU3MQU4A7GJDH4UA/"/>
+    <hyperlink ref="V51" r:id="rId70" location="" tooltip="" display="https://www.chvnoticias.cl/exclusivo-chv/todas-las-pruebas-fiscalia-hector-espinosa-pdi_20220828/"/>
+    <hyperlink ref="W51" r:id="rId71" location="" tooltip="" display="https://www.chilevision.cl/noticias/nacional/exdirector-general-de-la-pdi-hector-espinosa-fue-condenado-a-17-anos"/>
+    <hyperlink ref="U52" r:id="rId72" location="" tooltip="" display="https://www.ciperchile.cl/2023/05/26/escandalo-de-cuentas-corrientes-municipales-de-nuble-golpea-en-la-region-metropolitana-contraloria-obliga-a-san-bernardo-a-terminar-contrato/"/>
+    <hyperlink ref="U53" r:id="rId73" location="" tooltip="" display="https://www.latercera.com/earlyaccess/noticia/las-millonarias-transacciones-que-complican-al-alcalde-de-rancagua/GY4SPWLFPJDODKTTXDN7FR74B4/"/>
+    <hyperlink ref="V53" r:id="rId74" location="" tooltip="" display="https://radio.uchile.cl/2023/03/04/tras-allanamiento-a-alcalde-de-rancagua-expertos-en-transparencia-llaman-a-fortalecer-los-mecanismos-para-perseguir-la-corrupcion/"/>
+    <hyperlink ref="W53" r:id="rId75" location="" tooltip="" display="https://www.meganoticias.cl/nacional/442934-alcalde-rancagua-formalizacion-abril-delitos-corrupcion-juan-ramon-godoy-21-03-2024.html"/>
+    <hyperlink ref="X53" r:id="rId76" location="" tooltip="" display="https://www.cde.cl/cde-interpone-querella-criminal-contra-el-alcalde-de-rancagua-por-delitos-asociados-a-hechos-de-corrupcion/"/>
+    <hyperlink ref="U54" r:id="rId77" location="" tooltip="" display="https://radio.uchile.cl/2022/01/19/juzgado-de-pozo-almonte-declara-admisible-querella-contra-alcalde-richard-godoy-por-delitos-tributarios-que-ascenderian-a-mas-de-1300-millones-de-pesos/"/>
+    <hyperlink ref="V54" r:id="rId78" location="" tooltip="" display="https://www.soychile.cl/Iquique/Sociedad/2022/01/19/741037/pozo-querella-richard-godoy-evasion.aspx"/>
+    <hyperlink ref="U55" r:id="rId79" location="" tooltip="" display="https://www.cooperativa.cl/noticias/pais/judicial/denuncias-de-corrupcion/de-que-se-acusa-exactamente-a-daniel-jadue/2024-06-03/202306.html"/>
+    <hyperlink ref="V55" r:id="rId80" location="" tooltip="" display="https://www.cooperativa.cl/noticias/pais/politica/municipales/jadue-sospecha-de-doble-intencionalidad-de-proveedor-que-litiga-contra/2022-02-18/092208.html"/>
+    <hyperlink ref="W55" r:id="rId81" location="" tooltip="" display="https://www.pjud.cl/prensa-y-comunicaciones/noticias-del-poder-judicial/110088"/>
+    <hyperlink ref="U56" r:id="rId82" location="" tooltip="" display="https://www.biobiochile.cl/noticias/nacional/region-de-los-rios/2023/12/10/justicia-admite-querella-contra-alcaldesa-de-rio-bueno-por-malversacion-de-caudales-y-fraude-al-fisco.shtml"/>
+    <hyperlink ref="V56" r:id="rId83" location="" tooltip="" display="https://www.biobiochile.cl/noticias/nacional/region-de-los-rios/2024/10/15/allanan-municipio-de-rio-bueno-en-medio-de-investigacion-por-delitos-de-corrupcion.shtml"/>
+    <hyperlink ref="W56" r:id="rId84" location="" tooltip="" display="https://www.rioenlinea.cl/allanan-municipalidad-de-rio-bueno-por-caso-de-corrupcion-donde-se-investiga-a-alcaldesa-silva-y-exedil-reyes/"/>
+    <hyperlink ref="U57" r:id="rId85" location="" tooltip="" display="https://eltipografo.cl/2022/08/presentan-nueva-querella-por-fraude-al-fisco-contra-ex-alcalde-de-mostazal-sergio-medel-a"/>
+    <hyperlink ref="V57" r:id="rId86" location="" tooltip="" display="https://eltipografo.cl/2023/03/deficit-de-8-mil-millones-en-el-municipio-y-querellas-por-fraude-al-fisco-enfrenta-ex-alcalde-de-mostazal"/>
+    <hyperlink ref="W57" r:id="rId87" location="" tooltip="" display="https://www.biobiochile.cl/noticias/nacional/region-de-ohiggins/2022/08/11/municipio-prepara-querellas-tras-millonarias-irregularidades-en-san-francisco-de-mostazal.shtml"/>
+    <hyperlink ref="U58" r:id="rId88" location="" tooltip="" display="https://cooperativa.cl/noticias/pais/region-de-antofagasta/ex-alcaldesa-karen-rojo-condenada-a-cinco-anos-de-carcel-por-fraude-al/2022-03-24/135330.html"/>
+    <hyperlink ref="V58" r:id="rId89" location="" tooltip="" display="https://cooperativa.cl/noticias/pais/region-de-antofagasta/suprema-rechazo-recurso-de-nulidad-y-karen-rojo-debera-cumplir-pena-en/2022-03-23/155942.html"/>
+    <hyperlink ref="W58" r:id="rId90" location="" tooltip="" display="https://chile.as.com/actualidad/detencion-de-karen-rojo-a-que-partido-pertenecia-cuanto-dinero-robo-y-por-que-estaba-en-holanda-n/"/>
+    <hyperlink ref="U59" r:id="rId91" location="" tooltip="" display="https://www.emol.com/noticias/Nacional/2024/07/10/1136142/suprema-revoca-prision-preventiva.html"/>
+    <hyperlink ref="V59" r:id="rId92" location="" tooltip="" display="https://www.emol.com/noticias/Nacional/2024/06/07/1133101/cronologia-delitos-fiscal-puerto-natales.html"/>
+    <hyperlink ref="U60" r:id="rId93" location="" tooltip="" display="https://www.aduana.cl/megafraude-tributario-investigacion-de-aduanas-fue-clave-para/aduana/2023-12-21/174405.html"/>
+    <hyperlink ref="U61" r:id="rId94" location="" tooltip="" display="https://www.latercera.com/la-tercera-sabado/noticia/cientos-de-depositos-en-efectivo-y-una-cuenta-con-2300-millones-las-pruebas-que-complican-al-tronco-torrealba/LH674LXDYVBR3J5IDIFUCMRIXE/"/>
+    <hyperlink ref="V61" r:id="rId95" location="" tooltip="" display="https://www.ciperchile.cl/2023/05/20/caso-torrealba-detalles-de-gastos-de-campana-de-rn-que-fueron-financiados-con-dineros-de-vitacura/"/>
+    <hyperlink ref="W61" r:id="rId96" location="" tooltip="" display="https://www.elmostrador.cl/noticias/pais/2023/08/08/53-dias-tras-las-rejas-rechazan-solicitud-de-raul-torrealba-y-seguira-en-prision-preventiva/"/>
+    <hyperlink ref="X61" r:id="rId97" location="" tooltip="" display="https://www.latercera.com/nacional/noticia/vitacura-contraloria-objeta-mas-de-4500-millones-a-administracion-de-alcalde-torrealba-en-dos-anos/GK3X6GQBOVB5BFGOV4N52T3PXI/"/>
+    <hyperlink ref="U62" r:id="rId98" location="" tooltip="" display="https://www.latercera.com/nacional/noticia/caso-convenios-ministerio-publico-indaga-traspasos-a-fundaciones-por-mas-de-14-mil-millones-en-ocho-regiones/XUWDKEDIWNDXTOU3RCMSIVQZE4/"/>
+    <hyperlink ref="V62" r:id="rId99" location="" tooltip="" display="https://www.emol.com/noticias/Nacional/2023/07/06/1100220/fundacion-el-desarrollo-de-organizaciones.html"/>
+    <hyperlink ref="V63" r:id="rId100" location="" tooltip="" display="https://www.biobiochile.cl/noticias/nacional/region-de-la-araucania/2024/01/07/imputado-en-arista-caso-convenios-gobernador-de-la-araucania-luciano-rivas-confirma-su-repostulacion.shtml"/>
+    <hyperlink ref="W63" r:id="rId101" location="" tooltip="" display="https://www.cnnchile.com/pais/caso-convenios-fundacion-la-araucania-sueldo_20240901/"/>
+    <hyperlink ref="U64" r:id="rId102" location="" tooltip="" display="https://www.cnnchile.com/pais/destitucion-alcalde-rinconada-contraloria-irregularidades_20230606/"/>
+    <hyperlink ref="V64" r:id="rId103" location="" tooltip="" display="https://munirinconada.cl/alcalde-juan-galdames-se-refiere-a-juicio-de-cuentas-que-ordena-la-restitucion-de-300-millones/"/>
+    <hyperlink ref="U65" r:id="rId104" location="" tooltip="" display="https://www.latercera.com/earlyaccess/noticia/pintar-fachadas-turismo-creativo-y-ayuda-contra-el-suicidio-los-diversos-rubros-de-procultura-la-fundacion-con-mas-convenios-en-la-mira-de-fiscalia/PE7YFQCVMBAOTPHJPTUBEHVPUU/"/>
+    <hyperlink ref="V65" r:id="rId105" location="" tooltip="" display="https://www.ex-ante.cl/perfil-lo-que-hay-que-saber-de-alberto-larrain-sus-vinculos-politicos-y-las-indagaciones-a-la-fundacion-procultura-que-creo/"/>
+    <hyperlink ref="W65" r:id="rId106" location="" tooltip="" display="https://www.emol.com/noticias/Nacional/2024/10/10/1145174/chile-vamos-querella-gore-procultura.html"/>
+    <hyperlink ref="U66" r:id="rId107" location="" tooltip="" display="https://www.malaespinacheck.cl/pais/2023/08/04/fundacion-kimun-el-incumplido-contrato-por-1-200-millones/"/>
+    <hyperlink ref="U67" r:id="rId108" location="" tooltip="" display="https://www.malaespinacheck.cl/pais/2023/08/04/fundacion-kimun-el-incumplido-contrato-por-1-200-millones/"/>
+    <hyperlink ref="U68" r:id="rId109" location="" tooltip="" display="https://www.malaespinacheck.cl/pais/2024/01/03/los-14-detenidos-en-todo-chile-por-el-caso-convenios/"/>
+    <hyperlink ref="V68" r:id="rId110" location="" tooltip="" display="https://www.malaespinacheck.cl/pais/2023/08/04/fundacion-kimun-el-incumplido-contrato-por-1-200-millones/"/>
+    <hyperlink ref="U69" r:id="rId111" location="" tooltip="" display="https://cooperativa.cl/noticias/pais/judicial/denuncias-de-corrupcion/detenido-el-alcalde-de-algarrobo-se-entrego-frente-a-un-motel/2023-11-23/072824.html"/>
+    <hyperlink ref="V69" r:id="rId112" location="" tooltip="" display="https://www.biobiochile.cl/noticias/nacional/region-de-valparaiso/2024/06/04/desfalco-algarrobo-criptomonedas-propiedaes-estados-unidos.shtml"/>
+    <hyperlink ref="W69" r:id="rId113" location="" tooltip="" display="https://www.adnradio.cl/2024/12/05/fiscalia-cierra-investigacion-y-acusa-a-exalcalde-de-algarrobo-de-malversacion-y-lavado-de-activos-pedira-20-anos-de-carcel/"/>
+    <hyperlink ref="U70" r:id="rId114" location="" tooltip="" display="https://www.meganoticias.cl/amp/nacional/442953-mantencion-de-areas-verdes-alcalde-de-arica-firmo-trato-directo-por-1100-millones-con-empresa-creada-14-dias-antes.html"/>
+    <hyperlink ref="V70" r:id="rId115" location="" tooltip="" display="https://conecta2tv.cl/denuncian-ante-la-fiscalia-al-alcalde-de-arica-gerardo-espindola-por-posible-malversacion-de-caudales-publicos/"/>
+    <hyperlink ref="U72" r:id="rId116" location="" tooltip="" display="https://www.latercera.com/nacional/noticia/caso-convenios-ministerio-publico-indaga-traspasos-a-fundaciones-por-mas-de-14-mil-millones-en-ocho-regiones/XUWDKEDIWNDXTOU3RCMSIVQZE4/"/>
+    <hyperlink ref="V72" r:id="rId117" location="" tooltip="" display="https://radio.uchile.cl/2023/11/18/cde-se-querello-contra-fundaciones-en-la-araucania-por-fraude-al-gore/"/>
+    <hyperlink ref="W72" r:id="rId118" location="" tooltip="" display="https://www.cnnchile.com/pais/acusado-desviar-730-millones-mauricio-ojeda-formalizado-corrupcion-caso-convenios_20250101/"/>
+    <hyperlink ref="U73" r:id="rId119" location="" tooltip="" display="https://www.biobiochile.cl/noticias/nacional/region-del-maule/2024/03/11/pdi-allano-gobernacion-del-maule-en-medio-de-investigaciones-por-traspasos-a-urbanismo-social.shtml"/>
+    <hyperlink ref="V73" r:id="rId120" location="" tooltip="" display="https://www.biobiochile.cl/noticias/nacional/region-del-maule/2024/03/12/caso-convenios-jefe-de-control-interno-del-gore-maule-declaro-por-traspasos-a-urbanismo-social.shtml"/>
+    <hyperlink ref="U74" r:id="rId121" location="" tooltip="" display="https://www.latercera.com/nacional/noticia/caso-convenios-ministerio-publico-indaga-traspasos-a-fundaciones-por-mas-de-14-mil-millones-en-ocho-regiones/XUWDKEDIWNDXTOU3RCMSIVQZE4/"/>
+    <hyperlink ref="V74" r:id="rId122" location="" tooltip="" display="https://www.biobiochile.cl/noticias/nacional/region-de-antofagasta/2024/09/03/caso-convenios-formalizan-a-carlos-contreras-por-tres-delitos-de-fraude-al-fisco.shtml"/>
+    <hyperlink ref="U75" r:id="rId123" location="" tooltip="" display="https://radionuevomundo.cl/2023/07/18/gobernador-rivas-suma-al-caso-fundacion-local-traspasos-arbitrarios-a-coihue-y-a-universidades-de-la-araucania/"/>
+    <hyperlink ref="V75" r:id="rId124" location="" tooltip="" display="https://www.elciudadano.com/actualidad/el-entramado-de-ilicitos-de-platas-que-exploto-en-el-gore-araucania-y-que-repercute-en-renovacion-nacional/12/29/"/>
+    <hyperlink ref="W75" r:id="rId125" location="" tooltip="" display="https://resumen.cl/articulos/la-derecha-de-la-araucania-en-el-caso-fundaciones-las-irregularidades-de-espacio-coigue-que-llevaron-al-ministerio-de-justicia-a-solicitar-su-cierre"/>
+    <hyperlink ref="U76" r:id="rId126" location="" tooltip="" display="https://www.elmostrador.cl/dia/2023/03/31/exsubsecretaria-martorell-declaro-como-imputada-por-corrupcion-en-caso-motorola/"/>
+    <hyperlink ref="U77" r:id="rId127" location="" tooltip="" display="https://www.biobiochile.cl/noticias/nacional/region-del-bio-bio/2024/03/13/caso-convenios-allanan-empresa-que-facturo-356-millones-en-convenios-del-gore-bio-bio-y-bonhomia.shtml"/>
+    <hyperlink ref="V77" r:id="rId128" location="" tooltip="" display="https://resumen.cl/articulos/fundacion-contrato-con-dineros-del-gore-biobio-a-empresas-de-coordinador-de-programa-y-a-firma-donde-trabaja-su-hermano-y-su-madre-excandidata-republicana"/>
+    <hyperlink ref="W77" r:id="rId129" location="" tooltip="" display="https://cooperativa.cl/noticias/pais/region-del-biobio/detienen-a-lider-de-empresa-en-allanamiento-por-caso-convenios-pdi/2024-03-13/123002.html"/>
+    <hyperlink ref="U78" r:id="rId130" location="" tooltip="" display="https://www.24horas.cl/actualidad/politica/que-se-le-acusa-a-karina-oliva-emitir-boletas-falsas-defraudar-290-millones"/>
+    <hyperlink ref="U79" r:id="rId131" location="" tooltip="" display="https://www.latercera.com/nacional/noticia/caso-convenios-ministerio-publico-indaga-traspasos-a-fundaciones-por-mas-de-14-mil-millones-en-ocho-regiones/XUWDKEDIWNDXTOU3RCMSIVQZE4/"/>
+    <hyperlink ref="U80" r:id="rId132" location="" tooltip="" display="https://radio.uchile.cl/2023/11/28/755094/"/>
+    <hyperlink ref="V80" r:id="rId133" location="" tooltip="" display="https://elpais.com/chile/2023-08-05/caso-lenceria-la-telenovelesca-arista-de-la-trama-de-corrupcion-que-hace-temblar-la-politica-chilena.html"/>
+    <hyperlink ref="W80" r:id="rId134" location="" tooltip="" display="https://www.malaespinacheck.cl/pais/2024/01/03/los-14-detenidos-en-todo-chile-por-el-caso-convenios/"/>
+    <hyperlink ref="U81" r:id="rId135" location="" tooltip="" display="https://www.latercera.com/nacional/noticia/caso-convenios-ministerio-publico-indaga-traspasos-a-fundaciones-por-mas-de-14-mil-millones-en-ocho-regiones/XUWDKEDIWNDXTOU3RCMSIVQZE4/"/>
+    <hyperlink ref="V81" r:id="rId136" location="" tooltip="" display="https://www.meganoticias.cl/nacional/420687-nexos-politicos-gore-arica-fundacion-comprometidos-280-millones-25-7-2023.html"/>
+    <hyperlink ref="U82" r:id="rId137" location="" tooltip="" display="https://www.diarioconstitucional.cl/2023/06/20/ex-administrador-municipal-que-aprobo-el-financiamiento-para-que-alcalde-concejales-y-funcionarios-publicos-de-tierra-amarilla-emprendieran-viaje-turistico-a-la-habana-y-varadero-incurre-en-el-delit/"/>
+    <hyperlink ref="U83" r:id="rId138" location="" tooltip="" display="https://www.diarioviregion.cl/index.php/noticias/27551-ex-alcalde-de-san-fernando-juan-paulo-molina-condenado-por-fraude-al-fisco-reiterado"/>
+    <hyperlink ref="U84" r:id="rId139" location="" tooltip="" display="https://www.emol.com/noticias/Nacional/2023/11/15/1112897/daniel-jadue-declaracion-farmacias-populares.html"/>
+    <hyperlink ref="V84" r:id="rId140" location="" tooltip="" display="https://www.biobiochile.cl/noticias/nacional/chile/2024/04/02/fiscalia-formalizara-a-daniel-jadue-por-cohecho-administracion-desleal-fraude-al-fisco-y-estafa.shtml"/>
+    <hyperlink ref="U85" r:id="rId141" location="" tooltip="" display="https://www.elciudadano.com/reportaje-investigacion/fue-funcionario-de-confianza-de-felipe-alessandri-fiscalia-investiga-a-diputado-republicano-agustin-romero-por-fraude-al-fisco/03/07/"/>
+    <hyperlink ref="V85" r:id="rId142" location="" tooltip="" display="https://www.cooperativa.cl/noticias/pais/judicial/justicia-designo-a-ministra-de-fuero-para-cobrar-pago-de-horas-extras-a/2023-11-27/155546.html"/>
+    <hyperlink ref="W85" r:id="rId143" location="" tooltip="" display="https://interferencia.cl/articulos/corte-designa-ministra-de-fuero-para-cobrar-11-millones-que-diputado-republicano-recibio"/>
+    <hyperlink ref="U86" r:id="rId144" location="" tooltip="" display="https://www.malaespinacheck.cl/pais/2024/01/03/los-14-detenidos-en-todo-chile-por-el-caso-convenios/"/>
+    <hyperlink ref="V86" r:id="rId145" location="" tooltip="" display="https://www.elciudadano.com/actualidad/el-entramado-de-ilicitos-de-platas-que-exploto-en-el-gore-araucania-y-que-repercute-en-renovacion-nacional/12/29/"/>
+    <hyperlink ref="W86" r:id="rId146" location="" tooltip="" display="https://elperiodico.cl/contraloria-corrobora-participacion-de-exfuncionaria-del-gore-araucania-en-comision-que-aprobo-proyecto-de-fundacion-que-posteriormente-la-contrato/"/>
+    <hyperlink ref="U87" r:id="rId147" location="" tooltip="" display="https://www.emol.com/noticias/Nacional/2024/02/20/1122268/contraloria-caso-convenios-minvu-serviu.html"/>
+    <hyperlink ref="V87" r:id="rId148" location="" tooltip="" display="https://www.ex-ante.cl/confidencial-las-47-fundaciones-indagadas-por-justicia-en-el-caso-convenios/"/>
+    <hyperlink ref="W89" r:id="rId149" location="" tooltip="" display="https://www.biobiochile.cl/noticias/nacional/region-de-nuble/2023/10/15/cuentas-corrientes-tesorero-municipal-acusado-de-cohecho-logra-salida-alternativa-tras-donar-200-mil.shtml"/>
+    <hyperlink ref="X89" r:id="rId150" location="" tooltip="" display="https://www.biobiochile.cl/noticias/nacional/region-de-nuble/2023/04/25/causa-por-corrupcion-mantienen-prision-preventiva-para-alcalde-de-san-ignacio-y-un-operador-politico.shtml"/>
+    <hyperlink ref="V90" r:id="rId151" location="" tooltip="" display="https://www.emol.com/noticias/Nacional/2024/02/15/1121826/caso-cuentas-corrientes.html"/>
+    <hyperlink ref="U91" r:id="rId152" location="" tooltip="" display="https://www.emol.com/noticias/Nacional/2024/02/15/1121826/caso-cuentas-corrientes.html"/>
+    <hyperlink ref="V91" r:id="rId153" location="" tooltip="" display="https://radio.uchile.cl/2024/02/13/caso-cuentas-corrientes-detienen-a-alcalde-de-bulnes-por-delitos-economicos/"/>
+    <hyperlink ref="U92" r:id="rId154" location="" tooltip="" display="https://www.biobiochile.cl/noticias/nacional/region-de-nuble/2023/04/19/ex-udi-y-exasesor-de-sauerbaum-quien-es-el-operador-politico-investigado-por-corrupcion-en-nuble.shtml"/>
+    <hyperlink ref="V92" r:id="rId155" location="" tooltip="" display="https://www.biobiochile.cl/noticias/nacional/region-de-nuble/2023/04/25/causa-por-corrupcion-mantienen-prision-preventiva-para-alcalde-de-san-ignacio-y-un-operador-politico.shtml"/>
+    <hyperlink ref="U93" r:id="rId156" location="" tooltip="" display="https://www.t13.cl/noticia/politica/exclusivo-t13-millonario-pago-horas-extra-municipalidad-vitacura"/>
+    <hyperlink ref="V93" r:id="rId157" location="" tooltip="" display="https://www.latercera.com/la-tercera-pm/noticia/caso-torrealba-excontador-de-vitacura-apunta-a-que-platas-politicas-se-justificaban-bajo-el-rotulo-horas-extra/4XN3AQ3ZWNA4NHJZ23ZWE22DJI/"/>
+    <hyperlink ref="W93" r:id="rId158" location="" tooltip="" display="https://vergara240.udp.cl/municipalidad-las-condes-providencia-vitacura-horas-extraordinarias/"/>
+    <hyperlink ref="U94" r:id="rId159" location="" tooltip="" display="https://www.adnradio.cl/2025/05/08/operaban-desde-la-gestion-de-barriga-detienen-a-funcionarios-de-maipu-por-presunta-red-de-corrupcion-en-licencias-de-conducir/"/>
+    <hyperlink ref="V94" r:id="rId160" location="" tooltip="" display="https://www.elciudadano.com/chile/detienen-a-funcionarios-de-la-municipalidad-de-maipu-por-presunta-red-de-corrupcion-que-operaba-desde-gestion-de-barriga/05/08/"/>
+    <hyperlink ref="U95" r:id="rId161" location="" tooltip="" display="https://www.elmostrador.cl/noticias/pais/2024/12/27/auditoria-a-la-caja-pagadora-de-las-condes-45-mil-millones-en-horas-extras-y-25-causas-laborales/"/>
+    <hyperlink ref="V95" r:id="rId162" location="" tooltip="" display="https://www.cnnchile.com/pais/45-mil-millones-en-horas-extras-las-condes-concluye-auditoria-externa-y-apunta-a-revisar-corporaciones-municipales_20241227/"/>
+    <hyperlink ref="U96" r:id="rId163" location="" tooltip="" display="https://radio.uchile.cl/2024/01/17/en-suspenso-prision-preventiva-para-cathy-barriga-tribunal-dictara-cautelar-este-jueves/"/>
+    <hyperlink ref="V96" r:id="rId164" location="" tooltip="" display="https://lavozdemaipu.cl/cathy-barriga-ultimo-informe-con-peras-y-manzanas/"/>
+    <hyperlink ref="W96" r:id="rId165" location="" tooltip="" display="https://www.cooperativa.cl/noticias/pais/judicial/denuncias-de-corrupcion/cathy-barriga-quedo-en-prision-preventiva/2024-11-12/174907.html"/>
+    <hyperlink ref="U97" r:id="rId166" location="" tooltip="" display="https://www.latercera.com/la-tercera-pm/noticia/estafa-fraude-y-falsificacion-el-avance-en-la-investigacion-penal-en-las-condes-que-remece-a-la-administracion-penaloza/X7ZBPJAYLRA47LINUR5COTA5HY/"/>
+    <hyperlink ref="V97" r:id="rId167" location="" tooltip="" display="https://www.latercera.com/nacional/noticia/las-investigaciones-que-envuelven-al-municipio-de-las-condes-y-a-su-alcaldesa-daniela-penaloza/GYYWEXRFXNGJVKFJPOEWRQUB7I/"/>
+    <hyperlink ref="W97" r:id="rId168" location="" tooltip="" display="https://www.latercera.com/nacional/noticia/contraloria-sanciona-a-exalcaldesa-penaloza-por-compra-de-cesfam-en-las-condes-y-destituye-al-exdirector-de-control/"/>
+    <hyperlink ref="U98" r:id="rId169" location="" tooltip="" display="https://www.elmostrador.cl/noticias/pais/2024/12/12/el-ultimo-coletazo-del-caso-basura-exalcalde-luis-plaza-rn-condenado-por-fraude-al-fisco/"/>
+    <hyperlink ref="V98" r:id="rId170" location="" tooltip="" display="https://www.ciperchile.cl/2015/05/15/las-evidencias-contra-los-alcaldes-vittori-dc-y-plaza-rn-por-millonarios-negocios-irregulares-en-maipu-y-cerro-navia/"/>
+    <hyperlink ref="W98" r:id="rId171" location="" tooltip="" display="https://www.latercera.com/nacional/noticia/a-13-anos-de-que-se-iniciara-el-caso-condenan-a-exalcalde-luis-plaza-rn-por-fraude-al-fisco-en-ultima-arista-del-emblematico-caso-basura/TGWT6RCHCJHEBP5MVQXK2VL2AE/"/>
+    <hyperlink ref="X98" r:id="rId172" location="" tooltip="" display="https://www.adnradio.cl/2025/06/03/por-fraude-al-fisco-reiterado-en-caso-basura-exalcalde-luis-plaza-es-condenado-a-tres-anos-de-presidio-con-el-beneficio-de-libertad-vigilada/"/>
+    <hyperlink ref="U99" r:id="rId173" location="" tooltip="" display="https://www.elrancaguino.cl/2024/01/18/hasta-35-anos-de-carcel-y-el-pago-de-2-mil-millones-de-pesos-en-multas-arriesga-el-ex-alcalde-san-fernando-luis-berwart/"/>
+    <hyperlink ref="U100" r:id="rId174" location="" tooltip="" display="https://www.elcomunal.cl/comunales/2024/03/25/15-demandas-1-querella-y-17-solicitudes-de-arresto-por-deudas-de-1500-millones-del-municipio-de-la-higuera-sacuden-a-yerko-galleguillos/"/>
+    <hyperlink ref="V100" r:id="rId175" location="" tooltip="" display="https://www.elcomunal.cl/comunales/2024/10/04/contraloria-detecta-graves-irregularidades-en-municipalidad-de-la-higuera-y-envia-antecedentes-a-fiscalia/"/>
+    <hyperlink ref="U101" r:id="rId176" location="" tooltip="" display="https://www.biobiochile.cl/noticias/economia/actualidad-economica/2024/08/12/caso-audio-sii-se-querella-contra-luis-hermosilla-y-maria-villalobos-por-delitos-tributarios.shtml"/>
+    <hyperlink ref="V101" r:id="rId177" location="" tooltip="" display="https://www.publimetro.cl/noticias/2024/08/12/caso-audios-sii-se-querella-contra-luis-hermosilla-y-fernanda-villalobos-por-delitos-tributarios-y-fiscalia-solicita-formalizacion/"/>
+    <hyperlink ref="W101" r:id="rId178" location="" tooltip="" display="https://www.t13.cl/noticia/politica/caso-audios-las-pruebas-revelaciones-fiscalia-formalizacion-hermosilla-villalob-21-8-2024"/>
+    <hyperlink ref="U102" r:id="rId179" location="" tooltip="" display="https://www.biobiochile.cl/noticias/nacional/chile/2024/03/19/milicogate-dictan-procesamiento-contra-general-y-coroneles-r-por-presunto-fraude-de-519-millones.shtml"/>
+    <hyperlink ref="U103" r:id="rId180" location="" tooltip="" display="https://www.latercera.com/campuslt/noticia/luminarias-juzgado-de-garantia-de-iquique-condena-a-exconcejal-felipe-arenas-por-fraude-al-fisco-y-cohecho/OR3BBHZLARCULI7J5A22A66CSU/"/>
+    <hyperlink ref="V103" r:id="rId181" location="" tooltip="" display="https://iquiquetv.cl/2024/07/02/caso-luminarias-led-condenan-a-ex-concejal-felipe-arenas-por-cohecho-y-fraude-al-fisco/"/>
+    <hyperlink ref="U104" r:id="rId182" location="" tooltip="" display="https://www.latercera.com/opinion/noticia/columna-de-daniel-matamala-cual-elefante/EOAKP2PXWJHSFDBAKRXGVVS5ZA/"/>
+    <hyperlink ref="U105" r:id="rId183" location="" tooltip="" display="https://www.latercera.com/nacional/noticia/mas-de-200-millones-para-sanar-deudas-de-achifarp-y-pagos-a-funcionarios-fantasma-los-hitos-que-marcaron-el-primer-dia-de-formalizacion-del-alcalde-de-recoleta/YGFDCRRVJNFSXAA7KWM3YEIIUQ/"/>
+    <hyperlink ref="U106" r:id="rId184" location="" tooltip="" display="https://www.malaespinacheck.cl/pais/2024/01/29/quien-es-daniel-agusto-perez-el-exalcalde-formalizado-por-fraude-al-fisco/"/>
+    <hyperlink ref="V106" r:id="rId185" location="" tooltip="" display="https://www.biobiochile.cl/noticias/nacional/region-de-antofagasta/2024/01/24/son-11-casos-de-karen-rojo-formalizaron-a-exdelegado-de-pinera-en-antofagasta-por-fraude-al-fisco.shtml"/>
+    <hyperlink ref="U107" r:id="rId186" location="" tooltip="" display="https://www.latercera.com/nacional/noticia/exalcalde-de-nunoa-andres-zarhi-queda-con-arresto-domiciliario-nocturno-tras-formalizacion-por-fraude-al-fisco/64LJ53FVUJA4BIGCC4DMKIJWRU/"/>
+    <hyperlink ref="V107" r:id="rId187" location="" tooltip="" display="https://www.emol.com/noticias/Nacional/2024/02/27/1123065/decretan-arresto-domiciliario-nocturno-andreszarhi.html"/>
+    <hyperlink ref="U108" r:id="rId188" location="" tooltip="" display="https://www.biobiochile.cl/noticias/economia/actualidad-economica/2024/10/11/sii-se-querello-contra-los-hermanos-jalaff-por-facturas-falsas-y-provocar-dano-fiscal-por-161-744-998.shtml"/>
+    <hyperlink ref="U109" r:id="rId189" location="" tooltip="" display="https://www.meganoticias.cl/nacional/470071-cde-querella-exjefe-gobierno-digital-pinera-fraude-fisco-mega-investiga-17-12-2024.html"/>
+    <hyperlink ref="U110" r:id="rId190" location="" tooltip="" display="https://www.biobiochile.cl/noticias/nacional/region-de-la-araucania/2024/01/25/caso-cuentas-corrientes-contraloria-ordena-al-municipio-de-lautaro-restituir-cerca-de-80-millones.shtml"/>
+    <hyperlink ref="U111" r:id="rId191" location="" tooltip="" display="https://www.theclinic.cl/2024/02/27/pdi-acorrala-al-circulo-de-virginia-reginato-udi-acusa-a-exadministrador-municipal-de-millonarios-gastos-en-restaurantes-y-licorerias/"/>
+    <hyperlink ref="V111" r:id="rId192" location="" tooltip="" display="https://www.soychile.cl/valparaiso/sociedad/2024/01/22/844669/formalizacion-vina-boisier-fisco-reacciones.html"/>
+    <hyperlink ref="U112" r:id="rId193" location="" tooltip="" display="https://www.latercera.com/nacional/noticia/contraloria-detecta-dos-nuevos-municipios-involucrados-en-el-caso-cuentas-corrientes-y-deriva-antecedentes-a-la-fiscalia/5C3ZRUU3WFF4BFYSN4BG4GD7QE/"/>
+    <hyperlink ref="V112" r:id="rId194" location="" tooltip="" display="https://www.elsancarlino.cl/2024/06/contraloria-detecta-dos-nuevos.html"/>
+    <hyperlink ref="U113" r:id="rId195" location="" tooltip="" display="https://www.biobiochile.cl/noticias/nacional/region-de-los-rios/2024/02/15/cuentas-corrientes-rio-bueno-debera-restituir-76-millones-por-pagos-improcedentes-a-gestion-global.shtml"/>
+    <hyperlink ref="V113" r:id="rId196" location="" tooltip="" display="https://www.biobiochile.cl/noticias/nacional/region-de-los-rios/2023/09/24/caso-cuentas-corrientes-exalcalde-de-rio-bueno-declara-en-fiscalia-por-contratacion-de-gestion-global.shtml"/>
+    <hyperlink ref="U114" r:id="rId197" location="" tooltip="" display="https://www.canal9.cl/episodios/noticias/2024/07/26/alcalde-de-coronel-y-concejal-araya-seran-formalizados-por-caso-puerto-coronel"/>
+    <hyperlink ref="V114" r:id="rId198" location="" tooltip="" display="https://www.cooperativa.cl/noticias/pais/region-del-biobio/formalizaran-por-delitos-de-corrupcion-al-alcalde-de-coronel-y-a-otras/2024-07-26/084551.html"/>
+    <hyperlink ref="W114" r:id="rId199" location="" tooltip="" display="https://www.meganoticias.cl/nacional/459252-querella-alcalde-coronel-boris-chamorro-cohecho-pago-coimas-17-09-2024.html"/>
+    <hyperlink ref="X114" r:id="rId200" location="" tooltip="" display="https://eldesconcierto.cl/2024/12/16/arresto-domiciliario-nocturno-para-alcalde-electo-de-coronel-es-imputado-por-delitos-de-corrupcion?utm_term=Autofeed&amp;utm_medium=Social&amp;utm_source=Twitter#Echobox=1734388166"/>
+    <hyperlink ref="U115" r:id="rId201" location="" tooltip="" display="https://www.latercera.com/nacional/noticia/contraloria-detecta-dos-nuevos-municipios-involucrados-en-el-caso-cuentas-corrientes-y-deriva-antecedentes-a-la-fiscalia/5C3ZRUU3WFF4BFYSN4BG4GD7QE/"/>
+    <hyperlink ref="U116" r:id="rId202" location="" tooltip="" display="https://www.biobiochile.cl/noticias/nacional/region-de-los-lagos/2023/09/13/causa-por-corrupcion-y-lavado-de-activos-fiscal-explica-allanamiento-en-municipio-de-puerto-montt.shtml"/>
+    <hyperlink ref="V116" r:id="rId203" location="" tooltip="" display="https://www.diariodepuertomontt.cl/noticia/politica/2024/08/ter-ordena-la-remocion-del-alcalde-de-puerto-montt"/>
+    <hyperlink ref="W116" r:id="rId204" location="" tooltip="" display="https://www.emol.com/noticias/Nacional/2024/08/23/1140650/remueven-alcalde-de-puerto-montt.html"/>
+    <hyperlink ref="X116" r:id="rId205" location="" tooltip="" display="https://www.24horas.cl/regiones/zona-sur/los-lagos/alcalde-de-puerto-montt-destituido-notable-abandono-deberes"/>
+    <hyperlink ref="Y116" r:id="rId206" location="" tooltip="" display="https://www.biobiochile.cl/noticias/nacional/region-de-los-lagos/2024/10/23/exalcalde-de-puerto-montt-gervoy-paredes-queda-en-prision-preventiva-por-delitos-de-corrupcion.shtml"/>
+    <hyperlink ref="U119" r:id="rId207" location="" tooltip="" display="https://www.latercera.com/nacional/noticia/hassler-libre-de-cargos-cooper-cierra-investigacion-por-fallida-compra-de-clinica-sierra-bella-y-dice-que-no-hay-delito/"/>
+    <hyperlink ref="V119" r:id="rId208" location="" tooltip="" display="https://www.t13.cl/noticia/politica/alerta-teletrece-fiscal-cooper-decide-no-perseverar-investigacion-sierra-bella-26-5-2025?utm_source=Facebook&amp;utm_medium=Stack&amp;utm_campaign=Share13&amp;utm_id=share13"/>
+    <hyperlink ref="U120" r:id="rId209" location="" tooltip="" display="https://www.latercera.com/nacional/noticia/cde-se-querella-contra-el-diputado-joaquin-lavin-por-malversacion-de-caudales-publicos/"/>
+    <hyperlink ref="V120" r:id="rId210" location="" tooltip="" display="https://www.cnnchile.com/pais/30-facturas-22-millones-querella-cde-joaquin-lavin-leon_20250531/"/>
+    <hyperlink ref="W120" r:id="rId211" location="" tooltip="" display="https://www.biobiochile.cl/especial/bbcl-investiga/noticias/articulos/2025/05/30/facturas-falsas-en-el-congreso-cde-sale-a-la-caza-de-lavin-jr-y-su-circulo-de-hierro.shtml"/>
+    <hyperlink ref="U121" r:id="rId212" location="" tooltip="" display="https://www.biobiochile.cl/especial/bbcl-investiga/noticias/articulos/2025/03/21/libre-de-responsabilidad-carolina-toha-es-absuelta-en-dos-juicios-de-cuentas-por-irregularidades.shtml"/>
+    <hyperlink ref="U122" r:id="rId213" location="" tooltip="" display="https://www.biobiochile.cl/especial/bbcl-investiga/noticias/articulos/2025/03/28/fraude-en-gore-metropolitano-funcionario-acepto-facturas-falsas-de-empresa-por-mas-de-6-500-millones.shtml"/>
+    <hyperlink ref="V122" r:id="rId214" location="" tooltip="" display="https://www.latercera.com/pulso-pm/noticia/xepelin-se-querella-por-millonaria-estafa-con-facturas-falsas-vinculadas-al-gore-metropolitano/"/>
+    <hyperlink ref="W122" r:id="rId215" location="" tooltip="" display="https://www.elagora.net/millonario-fraude-en-gore-metropolitano/"/>
+    <hyperlink ref="U123" r:id="rId216" location="" tooltip="" display="https://contrapoderchile.cl/interponen-querella-criminal-en-contra-de-alcalde-sebastian-sichel-por-falsificacion-de-instrumento-publico/"/>
+    <hyperlink ref="U124" r:id="rId217" location="" tooltip="" display="https://reportea.cl/2025/11/29/los-secretos-politicos-de-yaber-arriendos-para-dos-parlamentarios-y-un-cheque-para-el-senador-gahona/"/>
+    <hyperlink ref="V124" r:id="rId218" location="" tooltip="" display="https://www.ciperchile.cl/2025/11/27/hija-de-senador-gahona-fue-contratada-por-sergio-yaber-en-el-cbr-de-puente-alto/"/>
+    <hyperlink ref="U125" r:id="rId219" location="" tooltip="" display="https://reportea.cl/2025/11/22/trama-bielorrusa-documento-del-bci-revela-pago-de-16-millones-de-sergio-yaber-al-senador-walker/"/>
+    <hyperlink ref="U126" r:id="rId220" location="" tooltip="" display="https://www.ciperchile.cl/2025/11/19/arista-bielorrusa-en-un-dialogo-pinchado-por-el-os7-el-conservador-yaber-dijo-que-le-entrego-17-millones-a-diputado-republicano/"/>
+    <hyperlink ref="U127" r:id="rId221" location="" tooltip="" display="https://contrapoderchile.cl/concejala-de-la-florida-rn-fue-contratada-en-el-municipio-de-santiago-y-ha-recibido-mas-de-8-millones-en-horas-extras/"/>
+    <hyperlink ref="U128" r:id="rId222" location="" tooltip="" display="https://www.adnradio.cl/2025/12/19/golpe-a-la-gestion-carter-contraloria-pide-devolver-fondos-pagados-a-cecilia-perez-su-exmarido-y-su-cunada-en-la-florida/"/>
+    <hyperlink ref="V128" r:id="rId223" location="" tooltip="" display="https://www.ciperchile.cl/2025/12/19/contraloria-revisa-trabajo-de-cecilia-perez-en-la-florida-solicita-devolucion-de-18-millones-por-labores-no-acreditadas/"/>
+    <hyperlink ref="U129" r:id="rId224" location="" tooltip="" display="https://contrapoderchile.cl/contraloria-confirma-que-francisco-orrego-devolvio-9-millones-a-la-municipalidad-de-la-florida-por-contratacion-irregular/"/>
   </hyperlinks>
   <pageMargins left="0.5" right="0.5" top="0.75" bottom="0.75" header="0.277778" footer="0.277778"/>
   <pageSetup firstPageNumber="1" fitToHeight="1" fitToWidth="1" scale="72" useFirstPageNumber="0" orientation="portrait" pageOrder="downThenOver"/>
